--- a/results/tables/DisplayBrightness/DisplayBrightness.xlsx
+++ b/results/tables/DisplayBrightness/DisplayBrightness.xlsx
@@ -1,28 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HamaKazu\Desktop\GradSchool\lab\experiment\DisplayBrightness\BackgroundDisplay\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HamaKazu\Desktop\GradSchool\lab\results\tables\DisplayBrightness\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86758ED-2D8E-432B-B0F1-35501636AD03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{5C750838-C35B-4502-A07E-7353115F065A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-3840" yWindow="-1872" windowWidth="30912" windowHeight="16896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FG_RGB_Trance" sheetId="8" r:id="rId1"/>
     <sheet name="FG補正OFF" sheetId="6" r:id="rId2"/>
     <sheet name="FGDisplay" sheetId="2" r:id="rId3"/>
-    <sheet name="BG_RGB_Trance" sheetId="7" r:id="rId4"/>
-    <sheet name="BGDisplay" sheetId="1" r:id="rId5"/>
-    <sheet name="FGLUMI" sheetId="5" r:id="rId6"/>
-    <sheet name="BGLUMI" sheetId="3" r:id="rId7"/>
-    <sheet name="BG補正OFF" sheetId="4" r:id="rId8"/>
+    <sheet name="画素値固定" sheetId="9" r:id="rId4"/>
+    <sheet name="BG_RGB_Trance" sheetId="7" r:id="rId5"/>
+    <sheet name="BGDisplay" sheetId="1" r:id="rId6"/>
+    <sheet name="FGLUMI" sheetId="5" r:id="rId7"/>
+    <sheet name="BGLUMI" sheetId="3" r:id="rId8"/>
+    <sheet name="BG補正OFF" sheetId="4" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="134">
   <si>
     <t>標準光</t>
     <rPh sb="0" eb="2">
@@ -538,6 +540,88 @@
     <t>10'</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>std</t>
+  </si>
+  <si>
+    <t>bg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>fg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 255</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 230</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 217</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 180</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 155</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 102</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 0</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Date</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 254</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 243</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 232</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 202</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 186</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 168</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 148</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 123</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 90</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -636,7 +720,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -684,6 +768,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -12579,11 +12668,11 @@
         <v>2</v>
       </c>
       <c r="O2">
-        <f t="shared" ref="O2:P2" si="0">ABS(H2-L2)</f>
+        <f>ABS(H2-L2)</f>
         <v>0</v>
       </c>
       <c r="P2">
-        <f t="shared" si="0"/>
+        <f>ABS(I2-M2)</f>
         <v>1</v>
       </c>
       <c r="Q2">
@@ -12591,11 +12680,11 @@
         <v>4</v>
       </c>
       <c r="R2">
-        <f t="shared" ref="R2:S2" si="1">O2^2</f>
+        <f>O2^2</f>
         <v>0</v>
       </c>
       <c r="S2">
-        <f t="shared" si="1"/>
+        <f>P2^2</f>
         <v>1</v>
       </c>
     </row>
@@ -12637,27 +12726,27 @@
         <v>31</v>
       </c>
       <c r="N3">
-        <f t="shared" ref="N3:N11" si="2">ABS(G3-K3)</f>
+        <f t="shared" ref="N3:N11" si="0">ABS(G3-K3)</f>
         <v>1</v>
       </c>
       <c r="O3">
-        <f t="shared" ref="O3:O11" si="3">ABS(H3-L3)</f>
+        <f t="shared" ref="O3:O11" si="1">ABS(H3-L3)</f>
         <v>2</v>
       </c>
       <c r="P3">
-        <f t="shared" ref="P3:P11" si="4">ABS(I3-M3)</f>
+        <f t="shared" ref="P3:P11" si="2">ABS(I3-M3)</f>
         <v>2</v>
       </c>
       <c r="Q3">
-        <f t="shared" ref="Q3:Q11" si="5">N3^2</f>
+        <f t="shared" ref="Q3:Q11" si="3">N3^2</f>
         <v>1</v>
       </c>
       <c r="R3">
-        <f t="shared" ref="R3:R11" si="6">O3^2</f>
+        <f t="shared" ref="R3:R11" si="4">O3^2</f>
         <v>4</v>
       </c>
       <c r="S3">
-        <f t="shared" ref="S3:S11" si="7">P3^2</f>
+        <f t="shared" ref="S3:S11" si="5">P3^2</f>
         <v>4</v>
       </c>
     </row>
@@ -12699,27 +12788,27 @@
         <v>50</v>
       </c>
       <c r="N4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="P4">
         <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="O4">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="P4">
+      <c r="R4">
         <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="Q4">
+        <v>4</v>
+      </c>
+      <c r="S4">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="R4">
-        <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="S4">
-        <f t="shared" si="7"/>
         <v>4</v>
       </c>
     </row>
@@ -12761,27 +12850,27 @@
         <v>34</v>
       </c>
       <c r="N5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P5">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="O5">
+      <c r="Q5">
         <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="P5">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="Q5">
+      <c r="S5">
         <f t="shared" si="5"/>
-        <v>4</v>
-      </c>
-      <c r="R5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <f t="shared" si="7"/>
         <v>4</v>
       </c>
     </row>
@@ -12823,27 +12912,27 @@
         <v>22</v>
       </c>
       <c r="N6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P6">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O6">
+        <v>3</v>
+      </c>
+      <c r="Q6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P6">
+      <c r="R6">
         <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="S6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <f t="shared" si="7"/>
         <v>9</v>
       </c>
     </row>
@@ -12885,27 +12974,27 @@
         <v>17</v>
       </c>
       <c r="N7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P7">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="O7">
+      <c r="Q7">
         <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="P7">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q7">
+      <c r="S7">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="R7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -12935,27 +13024,27 @@
         <v>115</v>
       </c>
       <c r="N8">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="P8">
         <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-      <c r="O8">
+        <v>3</v>
+      </c>
+      <c r="Q8">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="P8">
+        <v>144</v>
+      </c>
+      <c r="R8">
         <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="Q8">
+        <v>4</v>
+      </c>
+      <c r="S8">
         <f t="shared" si="5"/>
-        <v>144</v>
-      </c>
-      <c r="R8">
-        <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="S8">
-        <f t="shared" si="7"/>
         <v>9</v>
       </c>
     </row>
@@ -12994,27 +13083,27 @@
         <v>22</v>
       </c>
       <c r="N9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P9">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
         <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="P9">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q9">
+      <c r="S9">
         <f t="shared" si="5"/>
-        <v>4</v>
-      </c>
-      <c r="R9">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="S9">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -13053,27 +13142,27 @@
         <v>9</v>
       </c>
       <c r="N10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P10">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P10">
+      <c r="R10">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="S10">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -13112,27 +13201,27 @@
         <v>77</v>
       </c>
       <c r="N11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P11">
         <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="O11">
+        <v>2</v>
+      </c>
+      <c r="Q11">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="P11">
+      <c r="R11">
         <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="S11">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="R11">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="S11">
-        <f t="shared" si="7"/>
         <v>4</v>
       </c>
     </row>
@@ -13141,27 +13230,27 @@
         <v>86</v>
       </c>
       <c r="N12">
-        <f>AVERAGE(N2:N11)</f>
+        <f t="shared" ref="N12:S12" si="6">AVERAGE(N2:N11)</f>
         <v>2.2000000000000002</v>
       </c>
       <c r="O12">
-        <f t="shared" ref="O12:S12" si="8">AVERAGE(O2:O11)</f>
+        <f t="shared" si="6"/>
         <v>0.8</v>
       </c>
       <c r="P12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1.7</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="R12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1.4</v>
       </c>
       <c r="S12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>3.7</v>
       </c>
     </row>
@@ -13184,11 +13273,11 @@
         <v>4</v>
       </c>
       <c r="R13">
-        <f t="shared" ref="R13:S13" si="9">SQRT(R12)</f>
+        <f>SQRT(R12)</f>
         <v>1.1832159566199232</v>
       </c>
       <c r="S13">
-        <f t="shared" si="9"/>
+        <f>SQRT(S12)</f>
         <v>1.9235384061671346</v>
       </c>
     </row>
@@ -13346,11 +13435,11 @@
         <v>3</v>
       </c>
       <c r="O18">
-        <f t="shared" ref="O18:O27" si="10">ABS(H18-L18)</f>
+        <f t="shared" ref="O18:O27" si="7">ABS(H18-L18)</f>
         <v>0</v>
       </c>
       <c r="P18">
-        <f t="shared" ref="P18:P27" si="11">ABS(I18-M18)</f>
+        <f t="shared" ref="P18:P27" si="8">ABS(I18-M18)</f>
         <v>0</v>
       </c>
       <c r="Q18">
@@ -13358,11 +13447,11 @@
         <v>9</v>
       </c>
       <c r="R18">
-        <f t="shared" ref="R18:R27" si="12">O18^2</f>
+        <f t="shared" ref="R18:R27" si="9">O18^2</f>
         <v>0</v>
       </c>
       <c r="S18">
-        <f t="shared" ref="S18:S27" si="13">P18^2</f>
+        <f t="shared" ref="S18:S27" si="10">P18^2</f>
         <v>0</v>
       </c>
     </row>
@@ -13404,27 +13493,27 @@
         <v>34</v>
       </c>
       <c r="N19">
-        <f t="shared" ref="N19:N27" si="14">ABS(G19-K19)</f>
+        <f t="shared" ref="N19:N27" si="11">ABS(G19-K19)</f>
         <v>2</v>
       </c>
       <c r="O19">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" ref="Q19:Q27" si="12">N19^2</f>
+        <v>4</v>
+      </c>
+      <c r="R19">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="S19">
         <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-      <c r="P19">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <f t="shared" ref="Q19:Q27" si="15">N19^2</f>
-        <v>4</v>
-      </c>
-      <c r="R19">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-      <c r="S19">
-        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -13454,27 +13543,27 @@
         <v>54</v>
       </c>
       <c r="N20">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="O20">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="R20">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S20">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <f t="shared" si="11"/>
-        <v>2</v>
-      </c>
-      <c r="Q20">
-        <f t="shared" si="15"/>
-        <v>1</v>
-      </c>
-      <c r="R20">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <f t="shared" si="13"/>
         <v>4</v>
       </c>
     </row>
@@ -13507,27 +13596,27 @@
         <v>37</v>
       </c>
       <c r="N21">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
       <c r="O21">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="P21">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="12"/>
+        <v>9</v>
+      </c>
+      <c r="R21">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="S21">
         <f t="shared" si="10"/>
-        <v>2</v>
-      </c>
-      <c r="P21">
-        <f t="shared" si="11"/>
-        <v>2</v>
-      </c>
-      <c r="Q21">
-        <f t="shared" si="15"/>
-        <v>9</v>
-      </c>
-      <c r="R21">
-        <f t="shared" si="12"/>
-        <v>4</v>
-      </c>
-      <c r="S21">
-        <f t="shared" si="13"/>
         <v>4</v>
       </c>
     </row>
@@ -13560,27 +13649,27 @@
         <v>24</v>
       </c>
       <c r="N22">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="O22">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="R22">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S22">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="P22">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <f t="shared" si="15"/>
-        <v>1</v>
-      </c>
-      <c r="R22">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -13613,27 +13702,27 @@
         <v>18</v>
       </c>
       <c r="N23">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="P23">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
+      <c r="O23">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="Q23">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="R23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
+      <c r="R23">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="S23">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -13663,27 +13752,27 @@
         <v>118</v>
       </c>
       <c r="N24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>12</v>
       </c>
       <c r="O24">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="P24">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="Q24">
+        <f t="shared" si="12"/>
+        <v>144</v>
+      </c>
+      <c r="R24">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="S24">
         <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-      <c r="P24">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="Q24">
-        <f t="shared" si="15"/>
-        <v>144</v>
-      </c>
-      <c r="R24">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-      <c r="S24">
-        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -13713,27 +13802,27 @@
         <v>21</v>
       </c>
       <c r="N25">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="O25">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="P25">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
+      <c r="O25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
       <c r="Q25">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="R25">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -13763,27 +13852,27 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="P26">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="Q26">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="R26">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
+      <c r="R26">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="S26">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -13813,53 +13902,53 @@
         <v>81</v>
       </c>
       <c r="N27">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="O27">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="P27">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
+      <c r="O27">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
       <c r="Q27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="R27">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:19">
       <c r="N28">
-        <f>AVERAGE(N18:N27)</f>
+        <f t="shared" ref="N28:S28" si="13">AVERAGE(N18:N27)</f>
         <v>2.4</v>
       </c>
       <c r="O28">
-        <f t="shared" ref="O28:S28" si="16">AVERAGE(O18:O27)</f>
+        <f t="shared" si="13"/>
         <v>0.4</v>
       </c>
       <c r="P28">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0.8</v>
       </c>
       <c r="Q28">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>17</v>
       </c>
       <c r="R28">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0.6</v>
       </c>
       <c r="S28">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>1.2</v>
       </c>
     </row>
@@ -13873,11 +13962,11 @@
         <v>4.1231056256176606</v>
       </c>
       <c r="R29">
-        <f t="shared" ref="R29:S29" si="17">SQRT(R28)</f>
+        <f>SQRT(R28)</f>
         <v>0.7745966692414834</v>
       </c>
       <c r="S29">
-        <f t="shared" si="17"/>
+        <f>SQRT(S28)</f>
         <v>1.0954451150103321</v>
       </c>
     </row>
@@ -13912,14 +14001,14 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4"/>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19" t="s">
+      <c r="C1" s="22"/>
+      <c r="D1" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="19"/>
+      <c r="E1" s="22"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4"/>
@@ -15517,6 +15606,175 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E63BFBA-8482-4406-A3A3-55ADB73C3469}">
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="19.69921875" customWidth="1"/>
+    <col min="2" max="12" width="14.19921875" style="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="19">
+        <v>46098</v>
+      </c>
+      <c r="B3" s="20">
+        <v>30</v>
+      </c>
+      <c r="C3" s="20">
+        <v>25</v>
+      </c>
+      <c r="D3" s="20">
+        <v>19</v>
+      </c>
+      <c r="E3" s="20">
+        <v>15</v>
+      </c>
+      <c r="F3" s="20">
+        <v>9</v>
+      </c>
+      <c r="G3" s="20">
+        <v>6</v>
+      </c>
+      <c r="H3" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="19"/>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="19"/>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="19">
+        <v>46098</v>
+      </c>
+      <c r="B11" s="20">
+        <v>97</v>
+      </c>
+      <c r="C11" s="20">
+        <v>87</v>
+      </c>
+      <c r="D11" s="20">
+        <v>77</v>
+      </c>
+      <c r="E11" s="20">
+        <v>67</v>
+      </c>
+      <c r="F11" s="20">
+        <v>58</v>
+      </c>
+      <c r="G11" s="20">
+        <v>49</v>
+      </c>
+      <c r="H11" s="20">
+        <v>38</v>
+      </c>
+      <c r="I11" s="20">
+        <v>29</v>
+      </c>
+      <c r="J11" s="20">
+        <v>19</v>
+      </c>
+      <c r="K11" s="20">
+        <v>10</v>
+      </c>
+      <c r="L11" s="20">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50473ED6-92DB-49CB-BB73-3D59C4C4199E}">
   <dimension ref="A1:S31"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -15617,11 +15875,11 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <f t="shared" ref="O2:P2" si="0">ABS(H2-L2)</f>
+        <f>ABS(H2-L2)</f>
         <v>1</v>
       </c>
       <c r="P2">
-        <f t="shared" si="0"/>
+        <f>ABS(I2-M2)</f>
         <v>0</v>
       </c>
       <c r="Q2">
@@ -15629,11 +15887,11 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <f t="shared" ref="R2:S11" si="1">O2^2</f>
+        <f t="shared" ref="R2:S11" si="0">O2^2</f>
         <v>1</v>
       </c>
       <c r="S2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -15675,27 +15933,27 @@
         <v>17</v>
       </c>
       <c r="N3">
-        <f t="shared" ref="N3:N11" si="2">ABS(G3-K3)</f>
+        <f t="shared" ref="N3:N11" si="1">ABS(G3-K3)</f>
         <v>2</v>
       </c>
       <c r="O3">
-        <f t="shared" ref="O3:O11" si="3">ABS(H3-L3)</f>
+        <f t="shared" ref="O3:O11" si="2">ABS(H3-L3)</f>
         <v>2</v>
       </c>
       <c r="P3">
-        <f t="shared" ref="P3:P11" si="4">ABS(I3-M3)</f>
+        <f t="shared" ref="P3:P11" si="3">ABS(I3-M3)</f>
         <v>0</v>
       </c>
       <c r="Q3">
-        <f t="shared" ref="Q3:Q11" si="5">N3^2</f>
+        <f t="shared" ref="Q3:Q11" si="4">N3^2</f>
         <v>4</v>
       </c>
       <c r="R3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="S3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -15737,27 +15995,27 @@
         <v>29</v>
       </c>
       <c r="N4">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="O4">
         <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="O4">
+        <v>4</v>
+      </c>
+      <c r="P4">
         <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q4">
-        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="R4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="S4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -15799,27 +16057,27 @@
         <v>18</v>
       </c>
       <c r="N5">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="O5">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="O5">
+        <v>2</v>
+      </c>
+      <c r="P5">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="R5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="S5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -15861,27 +16119,27 @@
         <v>13</v>
       </c>
       <c r="N6">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="O6">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q6">
-        <f t="shared" si="5"/>
-        <v>4</v>
-      </c>
-      <c r="R6">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="S6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -15923,27 +16181,27 @@
         <v>11</v>
       </c>
       <c r="N7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="O7">
         <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="O7">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="P7">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="Q7">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
       <c r="R7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="S7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -15973,27 +16231,27 @@
         <v>69</v>
       </c>
       <c r="N8">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="O8">
         <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
-      <c r="O8">
+        <v>4</v>
+      </c>
+      <c r="P8">
         <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q8">
-        <f t="shared" si="5"/>
         <v>196</v>
       </c>
       <c r="R8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="S8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -16032,27 +16290,27 @@
         <v>15</v>
       </c>
       <c r="N9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O9">
         <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O9">
-        <f t="shared" si="3"/>
+      <c r="R9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="P9">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="Q9">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="S9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -16091,27 +16349,27 @@
         <v>7</v>
       </c>
       <c r="N10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="O10">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q10">
-        <f t="shared" si="5"/>
-        <v>9</v>
-      </c>
-      <c r="R10">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="S10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -16150,27 +16408,27 @@
         <v>44</v>
       </c>
       <c r="N11">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="O11">
         <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="O11">
+        <v>4</v>
+      </c>
+      <c r="P11">
         <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="R11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="S11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -16179,27 +16437,27 @@
         <v>86</v>
       </c>
       <c r="N12">
-        <f>AVERAGE(N2:N11)</f>
+        <f t="shared" ref="N12:S12" si="5">AVERAGE(N2:N11)</f>
         <v>3.5</v>
       </c>
       <c r="O12">
-        <f t="shared" ref="O12:P12" si="6">AVERAGE(O2:O11)</f>
+        <f t="shared" si="5"/>
         <v>2.2999999999999998</v>
       </c>
       <c r="P12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.8</v>
       </c>
       <c r="Q12">
-        <f t="shared" ref="Q12" si="7">AVERAGE(Q2:Q11)</f>
+        <f t="shared" si="5"/>
         <v>27.3</v>
       </c>
       <c r="R12">
-        <f t="shared" ref="R12" si="8">AVERAGE(R2:R11)</f>
+        <f t="shared" si="5"/>
         <v>6.9</v>
       </c>
       <c r="S12">
-        <f t="shared" ref="S12" si="9">AVERAGE(S2:S11)</f>
+        <f t="shared" si="5"/>
         <v>1.2</v>
       </c>
     </row>
@@ -16222,11 +16480,11 @@
         <v>5.2249401910452526</v>
       </c>
       <c r="R13">
-        <f t="shared" ref="R13:S13" si="10">SQRT(R12)</f>
+        <f>SQRT(R12)</f>
         <v>2.6267851073127395</v>
       </c>
       <c r="S13">
-        <f t="shared" si="10"/>
+        <f>SQRT(S12)</f>
         <v>1.0954451150103321</v>
       </c>
     </row>
@@ -16384,11 +16642,11 @@
         <v>0</v>
       </c>
       <c r="O18">
-        <f t="shared" ref="O18:O27" si="11">ABS(H18-L18)</f>
+        <f t="shared" ref="O18:O27" si="6">ABS(H18-L18)</f>
         <v>0</v>
       </c>
       <c r="P18">
-        <f t="shared" ref="P18:P27" si="12">ABS(I18-M18)</f>
+        <f t="shared" ref="P18:P27" si="7">ABS(I18-M18)</f>
         <v>1</v>
       </c>
       <c r="Q18">
@@ -16396,11 +16654,11 @@
         <v>0</v>
       </c>
       <c r="R18">
-        <f t="shared" ref="R18:R27" si="13">O18^2</f>
+        <f t="shared" ref="R18:R27" si="8">O18^2</f>
         <v>0</v>
       </c>
       <c r="S18">
-        <f t="shared" ref="S18:S27" si="14">P18^2</f>
+        <f t="shared" ref="S18:S27" si="9">P18^2</f>
         <v>1</v>
       </c>
     </row>
@@ -16442,27 +16700,27 @@
         <v>17</v>
       </c>
       <c r="N19">
-        <f t="shared" ref="N19:N27" si="15">ABS(G19-K19)</f>
+        <f t="shared" ref="N19:N27" si="10">ABS(G19-K19)</f>
         <v>1</v>
       </c>
       <c r="O19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="P19">
-        <f t="shared" si="12"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q19">
-        <f t="shared" ref="Q19:Q27" si="16">N19^2</f>
+        <f t="shared" ref="Q19:Q27" si="11">N19^2</f>
         <v>1</v>
       </c>
       <c r="R19">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
       <c r="S19">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -16492,27 +16750,27 @@
         <v>29</v>
       </c>
       <c r="N20">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
       <c r="O20">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="P20">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q20">
         <f t="shared" si="11"/>
-        <v>3</v>
-      </c>
-      <c r="P20">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="Q20">
-        <f t="shared" si="16"/>
         <v>25</v>
       </c>
       <c r="R20">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="S20">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -16542,27 +16800,27 @@
         <v>18</v>
       </c>
       <c r="N21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="O21">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="P21">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="Q21">
         <f t="shared" si="11"/>
-        <v>2</v>
-      </c>
-      <c r="P21">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-      <c r="Q21">
-        <f t="shared" si="16"/>
         <v>16</v>
       </c>
       <c r="R21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
       <c r="S21">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -16592,27 +16850,27 @@
         <v>13</v>
       </c>
       <c r="N22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="O22">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="Q22">
         <f t="shared" si="11"/>
+        <v>4</v>
+      </c>
+      <c r="R22">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="P22">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-      <c r="Q22">
-        <f t="shared" si="16"/>
-        <v>4</v>
-      </c>
-      <c r="R22">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
       <c r="S22">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -16642,27 +16900,27 @@
         <v>11</v>
       </c>
       <c r="N23">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="O23">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="P23">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="Q23">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="P23">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-      <c r="Q23">
-        <f t="shared" si="16"/>
-        <v>4</v>
-      </c>
       <c r="R23">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="S23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -16692,27 +16950,27 @@
         <v>69</v>
       </c>
       <c r="N24">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>12</v>
       </c>
       <c r="O24">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="P24">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="Q24">
         <f t="shared" si="11"/>
-        <v>4</v>
-      </c>
-      <c r="P24">
-        <f t="shared" si="12"/>
-        <v>2</v>
-      </c>
-      <c r="Q24">
-        <f t="shared" si="16"/>
         <v>144</v>
       </c>
       <c r="R24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="S24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
     </row>
@@ -16742,27 +17000,27 @@
         <v>15</v>
       </c>
       <c r="N25">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="O25">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="P25">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="Q25">
         <f t="shared" si="11"/>
-        <v>2</v>
-      </c>
-      <c r="P25">
-        <f t="shared" si="12"/>
-        <v>3</v>
-      </c>
-      <c r="Q25">
-        <f t="shared" si="16"/>
         <v>4</v>
       </c>
       <c r="R25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
       <c r="S25">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
     </row>
@@ -16792,27 +17050,27 @@
         <v>6</v>
       </c>
       <c r="N26">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="O26">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="Q26">
         <f t="shared" si="11"/>
+        <v>4</v>
+      </c>
+      <c r="R26">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="P26">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-      <c r="Q26">
-        <f t="shared" si="16"/>
-        <v>4</v>
-      </c>
-      <c r="R26">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
       <c r="S26">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -16842,53 +17100,53 @@
         <v>44</v>
       </c>
       <c r="N27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
       <c r="O27">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="P27">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q27">
         <f t="shared" si="11"/>
-        <v>5</v>
-      </c>
-      <c r="P27">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="Q27">
-        <f t="shared" si="16"/>
         <v>36</v>
       </c>
       <c r="R27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>25</v>
       </c>
       <c r="S27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:19">
       <c r="N28">
-        <f>AVERAGE(N18:N27)</f>
+        <f t="shared" ref="N28:S28" si="12">AVERAGE(N18:N27)</f>
         <v>3.6</v>
       </c>
       <c r="O28">
-        <f t="shared" ref="O28:S28" si="17">AVERAGE(O18:O27)</f>
+        <f t="shared" si="12"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="P28">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="Q28">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>23.8</v>
       </c>
       <c r="R28">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>7.8</v>
       </c>
       <c r="S28">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>1.8</v>
       </c>
     </row>
@@ -16902,11 +17160,11 @@
         <v>4.8785243670601872</v>
       </c>
       <c r="R29">
-        <f t="shared" ref="R29:S29" si="18">SQRT(R28)</f>
+        <f>SQRT(R28)</f>
         <v>2.7928480087537881</v>
       </c>
       <c r="S29">
-        <f t="shared" si="18"/>
+        <f>SQRT(S28)</f>
         <v>1.3416407864998738</v>
       </c>
     </row>
@@ -16934,7 +17192,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q89"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -19017,7 +19275,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{748D88B3-AB89-451F-B4F0-D6322845623C}">
   <dimension ref="A1:AF20"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -20043,7 +20301,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4F1D99B-35E9-4F54-9502-3DA711A1E317}">
   <dimension ref="A1:AF25"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -21174,21 +21432,21 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F91A220-ECA8-426C-9CB4-6411C694E3C1}">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4"/>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19" t="s">
+      <c r="C1" s="22"/>
+      <c r="D1" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="19"/>
+      <c r="E1" s="22"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4"/>

--- a/results/tables/DisplayBrightness/DisplayBrightness.xlsx
+++ b/results/tables/DisplayBrightness/DisplayBrightness.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HamaKazu\Desktop\GradSchool\lab\results\tables\DisplayBrightness\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{5C750838-C35B-4502-A07E-7353115F065A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79CC001A-DE68-4029-80C9-26739223474C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3840" yWindow="-1872" windowWidth="30912" windowHeight="16896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5856" yWindow="2724" windowWidth="17280" windowHeight="8880" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FG_RGB_Trance" sheetId="8" r:id="rId1"/>
@@ -24,7 +24,6 @@
     <sheet name="BG補正OFF" sheetId="4" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -15607,7 +15606,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E63BFBA-8482-4406-A3A3-55ADB73C3469}">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="19.69921875" customWidth="1"/>
@@ -15672,7 +15671,30 @@
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="19"/>
+      <c r="A4" s="19">
+        <v>46103</v>
+      </c>
+      <c r="B4" s="20">
+        <v>30</v>
+      </c>
+      <c r="C4" s="20">
+        <v>26</v>
+      </c>
+      <c r="D4" s="20">
+        <v>20</v>
+      </c>
+      <c r="E4" s="20">
+        <v>16</v>
+      </c>
+      <c r="F4" s="20">
+        <v>9</v>
+      </c>
+      <c r="G4" s="20">
+        <v>6</v>
+      </c>
+      <c r="H4" s="20">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="19"/>
@@ -15765,6 +15787,44 @@
         <v>10</v>
       </c>
       <c r="L11" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="19">
+        <v>46103</v>
+      </c>
+      <c r="B12" s="20">
+        <v>99</v>
+      </c>
+      <c r="C12" s="20">
+        <v>89</v>
+      </c>
+      <c r="D12" s="20">
+        <v>79</v>
+      </c>
+      <c r="E12" s="20">
+        <v>69</v>
+      </c>
+      <c r="F12" s="20">
+        <v>60</v>
+      </c>
+      <c r="G12" s="20">
+        <v>50</v>
+      </c>
+      <c r="H12" s="20">
+        <v>39</v>
+      </c>
+      <c r="I12" s="20">
+        <v>30</v>
+      </c>
+      <c r="J12" s="20">
+        <v>20</v>
+      </c>
+      <c r="K12" s="20">
+        <v>10</v>
+      </c>
+      <c r="L12" s="20">
         <v>0</v>
       </c>
     </row>

--- a/results/tables/DisplayBrightness/DisplayBrightness.xlsx
+++ b/results/tables/DisplayBrightness/DisplayBrightness.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HamaKazu\Desktop\GradSchool\lab\results\tables\DisplayBrightness\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79CC001A-DE68-4029-80C9-26739223474C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92290D6B-4421-4D5C-8275-EAB612036CAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5856" yWindow="2724" windowWidth="17280" windowHeight="8880" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FG_RGB_Trance" sheetId="8" r:id="rId1"/>
@@ -15606,7 +15606,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E63BFBA-8482-4406-A3A3-55ADB73C3469}">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="19.69921875" customWidth="1"/>
@@ -15697,7 +15697,30 @@
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="19"/>
+      <c r="A5" s="19">
+        <v>46105</v>
+      </c>
+      <c r="B5" s="20">
+        <v>29</v>
+      </c>
+      <c r="C5" s="20">
+        <v>25</v>
+      </c>
+      <c r="D5" s="20">
+        <v>19</v>
+      </c>
+      <c r="E5" s="20">
+        <v>16</v>
+      </c>
+      <c r="F5" s="20">
+        <v>9</v>
+      </c>
+      <c r="G5" s="20">
+        <v>6</v>
+      </c>
+      <c r="H5" s="20">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
@@ -15825,6 +15848,44 @@
         <v>10</v>
       </c>
       <c r="L12" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="19">
+        <v>46105</v>
+      </c>
+      <c r="B13" s="20">
+        <v>97</v>
+      </c>
+      <c r="C13" s="20">
+        <v>87</v>
+      </c>
+      <c r="D13" s="20">
+        <v>78</v>
+      </c>
+      <c r="E13" s="20">
+        <v>67</v>
+      </c>
+      <c r="F13" s="20">
+        <v>58</v>
+      </c>
+      <c r="G13" s="20">
+        <v>49</v>
+      </c>
+      <c r="H13" s="20">
+        <v>38</v>
+      </c>
+      <c r="I13" s="20">
+        <v>29</v>
+      </c>
+      <c r="J13" s="20">
+        <v>19</v>
+      </c>
+      <c r="K13" s="20">
+        <v>9</v>
+      </c>
+      <c r="L13" s="20">
         <v>0</v>
       </c>
     </row>

--- a/results/tables/DisplayBrightness/DisplayBrightness.xlsx
+++ b/results/tables/DisplayBrightness/DisplayBrightness.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HamaKazu\Desktop\GradSchool\lab\results\tables\DisplayBrightness\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92290D6B-4421-4D5C-8275-EAB612036CAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF778A59-94AA-47E7-8EDE-A04940E97A34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FG_RGB_Trance" sheetId="8" r:id="rId1"/>
@@ -15606,7 +15606,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E63BFBA-8482-4406-A3A3-55ADB73C3469}">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="19.69921875" customWidth="1"/>
@@ -15723,126 +15723,114 @@
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" t="s">
-        <v>113</v>
+      <c r="A6" s="19">
+        <v>46108</v>
+      </c>
+      <c r="B6" s="20">
+        <v>31</v>
+      </c>
+      <c r="C6" s="20">
+        <v>27</v>
+      </c>
+      <c r="D6" s="20">
+        <v>21</v>
+      </c>
+      <c r="E6" s="20">
+        <v>17</v>
+      </c>
+      <c r="F6" s="20">
+        <v>11</v>
+      </c>
+      <c r="G6" s="20">
+        <v>7</v>
+      </c>
+      <c r="H6" s="20">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
-      <c r="A9" t="s">
+    <row r="10" spans="1:12">
+      <c r="A10" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="21" t="s">
+    <row r="11" spans="1:12">
+      <c r="A11" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B11" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F11" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I11" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J11" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K11" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="L11" s="4" t="s">
         <v>123</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="19">
-        <v>46098</v>
-      </c>
-      <c r="B11" s="20">
-        <v>97</v>
-      </c>
-      <c r="C11" s="20">
-        <v>87</v>
-      </c>
-      <c r="D11" s="20">
-        <v>77</v>
-      </c>
-      <c r="E11" s="20">
-        <v>67</v>
-      </c>
-      <c r="F11" s="20">
-        <v>58</v>
-      </c>
-      <c r="G11" s="20">
-        <v>49</v>
-      </c>
-      <c r="H11" s="20">
-        <v>38</v>
-      </c>
-      <c r="I11" s="20">
-        <v>29</v>
-      </c>
-      <c r="J11" s="20">
-        <v>19</v>
-      </c>
-      <c r="K11" s="20">
-        <v>10</v>
-      </c>
-      <c r="L11" s="20">
-        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="19">
-        <v>46103</v>
+        <v>46098</v>
       </c>
       <c r="B12" s="20">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C12" s="20">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D12" s="20">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E12" s="20">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F12" s="20">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G12" s="20">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H12" s="20">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I12" s="20">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J12" s="20">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K12" s="20">
         <v>10</v>
@@ -15853,39 +15841,115 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="19">
+        <v>46103</v>
+      </c>
+      <c r="B13" s="20">
+        <v>99</v>
+      </c>
+      <c r="C13" s="20">
+        <v>89</v>
+      </c>
+      <c r="D13" s="20">
+        <v>79</v>
+      </c>
+      <c r="E13" s="20">
+        <v>69</v>
+      </c>
+      <c r="F13" s="20">
+        <v>60</v>
+      </c>
+      <c r="G13" s="20">
+        <v>50</v>
+      </c>
+      <c r="H13" s="20">
+        <v>39</v>
+      </c>
+      <c r="I13" s="20">
+        <v>30</v>
+      </c>
+      <c r="J13" s="20">
+        <v>20</v>
+      </c>
+      <c r="K13" s="20">
+        <v>10</v>
+      </c>
+      <c r="L13" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="19">
         <v>46105</v>
       </c>
-      <c r="B13" s="20">
+      <c r="B14" s="20">
         <v>97</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C14" s="20">
         <v>87</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D14" s="20">
         <v>78</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E14" s="20">
         <v>67</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F14" s="20">
         <v>58</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G14" s="20">
         <v>49</v>
       </c>
-      <c r="H13" s="20">
+      <c r="H14" s="20">
         <v>38</v>
       </c>
-      <c r="I13" s="20">
+      <c r="I14" s="20">
         <v>29</v>
       </c>
-      <c r="J13" s="20">
+      <c r="J14" s="20">
         <v>19</v>
       </c>
-      <c r="K13" s="20">
+      <c r="K14" s="20">
         <v>9</v>
       </c>
-      <c r="L13" s="20">
+      <c r="L14" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="19">
+        <v>46108</v>
+      </c>
+      <c r="B15" s="20">
+        <v>102</v>
+      </c>
+      <c r="C15" s="20">
+        <v>94</v>
+      </c>
+      <c r="D15" s="20">
+        <v>84</v>
+      </c>
+      <c r="E15" s="20">
+        <v>74</v>
+      </c>
+      <c r="F15" s="20">
+        <v>64</v>
+      </c>
+      <c r="G15" s="20">
+        <v>55</v>
+      </c>
+      <c r="H15" s="20">
+        <v>44</v>
+      </c>
+      <c r="I15" s="20">
+        <v>34</v>
+      </c>
+      <c r="J15" s="20">
+        <v>23</v>
+      </c>
+      <c r="K15" s="20">
+        <v>11</v>
+      </c>
+      <c r="L15" s="20">
         <v>0</v>
       </c>
     </row>

--- a/results/tables/DisplayBrightness/DisplayBrightness.xlsx
+++ b/results/tables/DisplayBrightness/DisplayBrightness.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HamaKazu\Desktop\GradSchool\lab\results\tables\DisplayBrightness\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF778A59-94AA-47E7-8EDE-A04940E97A34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58B05B98-F478-4B94-8A02-26EF3A52301D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FG_RGB_Trance" sheetId="8" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="134">
   <si>
     <t>標準光</t>
     <rPh sb="0" eb="2">
@@ -626,9 +626,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="176" formatCode="0.000_ "/>
     <numFmt numFmtId="177" formatCode="0.0_ "/>
+    <numFmt numFmtId="181" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -719,7 +720,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -767,13 +768,23 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -14000,14 +14011,14 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4"/>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22" t="s">
+      <c r="C1" s="20"/>
+      <c r="D1" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="22"/>
+      <c r="E1" s="20"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4"/>
@@ -15606,11 +15617,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E63BFBA-8482-4406-A3A3-55ADB73C3469}">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="19.69921875" customWidth="1"/>
-    <col min="2" max="12" width="14.19921875" style="20" customWidth="1"/>
+    <col min="2" max="12" width="14.19921875" style="19" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -15619,337 +15630,612 @@
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="16" t="s">
         <v>123</v>
       </c>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="19">
+      <c r="A3" s="22">
         <v>46098</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="21">
         <v>30</v>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="21">
         <v>25</v>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="21">
         <v>19</v>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="21">
         <v>15</v>
       </c>
-      <c r="F3" s="20">
+      <c r="F3" s="21">
         <v>9</v>
       </c>
-      <c r="G3" s="20">
+      <c r="G3" s="21">
         <v>6</v>
       </c>
-      <c r="H3" s="20">
+      <c r="H3" s="21">
         <v>0</v>
       </c>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="19">
+      <c r="A4" s="22">
         <v>46103</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="21">
         <v>30</v>
       </c>
-      <c r="C4" s="20">
+      <c r="C4" s="21">
         <v>26</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="21">
         <v>20</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="21">
         <v>16</v>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="21">
         <v>9</v>
       </c>
-      <c r="G4" s="20">
+      <c r="G4" s="21">
         <v>6</v>
       </c>
-      <c r="H4" s="20">
+      <c r="H4" s="21">
         <v>0</v>
       </c>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="19">
+      <c r="A5" s="22">
         <v>46105</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="21">
         <v>29</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="21">
         <v>25</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="21">
         <v>19</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="21">
         <v>16</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="21">
         <v>9</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="21">
         <v>6</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5" s="21">
         <v>0</v>
       </c>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="21"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="19">
+      <c r="A6" s="22">
         <v>46108</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="21">
         <v>31</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="21">
         <v>27</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="21">
         <v>21</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="21">
         <v>17</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="21">
         <v>11</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="21">
         <v>7</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="21">
         <v>0</v>
       </c>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="21"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" t="s">
+      <c r="A7" s="23">
+        <v>46112</v>
+      </c>
+      <c r="B7" s="14">
+        <v>29</v>
+      </c>
+      <c r="C7" s="14">
+        <v>25</v>
+      </c>
+      <c r="D7" s="14">
+        <v>19</v>
+      </c>
+      <c r="E7" s="14">
+        <v>15</v>
+      </c>
+      <c r="F7" s="14">
+        <v>9</v>
+      </c>
+      <c r="G7" s="14">
+        <v>5</v>
+      </c>
+      <c r="H7" s="14">
+        <v>0</v>
+      </c>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="21" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" t="s">
+      <c r="B8" s="21">
+        <f>AVERAGE(B3:B7)</f>
+        <v>29.8</v>
+      </c>
+      <c r="C8" s="21">
+        <f t="shared" ref="C8:H8" si="0">AVERAGE(C3:C7)</f>
+        <v>25.6</v>
+      </c>
+      <c r="D8" s="21">
+        <f t="shared" si="0"/>
+        <v>19.600000000000001</v>
+      </c>
+      <c r="E8" s="21">
+        <f t="shared" si="0"/>
+        <v>15.8</v>
+      </c>
+      <c r="F8" s="21">
+        <f t="shared" si="0"/>
+        <v>9.4</v>
+      </c>
+      <c r="G8" s="21">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="H8" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="21"/>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="14" t="s">
         <v>114</v>
       </c>
+      <c r="B9" s="24">
+        <f>_xlfn.STDEV.P(B3:B7)</f>
+        <v>0.74833147735478822</v>
+      </c>
+      <c r="C9" s="24">
+        <f t="shared" ref="C9:H9" si="1">_xlfn.STDEV.P(C3:C7)</f>
+        <v>0.79999999999999993</v>
+      </c>
+      <c r="D9" s="24">
+        <f t="shared" si="1"/>
+        <v>0.79999999999999993</v>
+      </c>
+      <c r="E9" s="24">
+        <f t="shared" si="1"/>
+        <v>0.74833147735478822</v>
+      </c>
+      <c r="F9" s="24">
+        <f t="shared" si="1"/>
+        <v>0.79999999999999993</v>
+      </c>
+      <c r="G9" s="24">
+        <f t="shared" si="1"/>
+        <v>0.63245553203367588</v>
+      </c>
+      <c r="H9" s="24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="21"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" t="s">
-        <v>116</v>
-      </c>
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="21"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="21"/>
+      <c r="L11" s="21"/>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B12" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C12" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D12" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E12" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F12" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G12" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H12" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I12" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="J12" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K12" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="L11" s="4" t="s">
+      <c r="L12" s="16" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="19">
+    <row r="13" spans="1:12">
+      <c r="A13" s="22">
         <v>46098</v>
       </c>
-      <c r="B12" s="20">
+      <c r="B13" s="21">
         <v>97</v>
       </c>
-      <c r="C12" s="20">
+      <c r="C13" s="21">
         <v>87</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D13" s="21">
         <v>77</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E13" s="21">
         <v>67</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F13" s="21">
         <v>58</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G13" s="21">
         <v>49</v>
       </c>
-      <c r="H12" s="20">
+      <c r="H13" s="21">
         <v>38</v>
       </c>
-      <c r="I12" s="20">
+      <c r="I13" s="21">
         <v>29</v>
       </c>
-      <c r="J12" s="20">
+      <c r="J13" s="21">
         <v>19</v>
       </c>
-      <c r="K12" s="20">
+      <c r="K13" s="21">
         <v>10</v>
       </c>
-      <c r="L12" s="20">
+      <c r="L13" s="21">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="19">
+    <row r="14" spans="1:12">
+      <c r="A14" s="22">
         <v>46103</v>
       </c>
-      <c r="B13" s="20">
+      <c r="B14" s="21">
         <v>99</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C14" s="21">
         <v>89</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D14" s="21">
         <v>79</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E14" s="21">
         <v>69</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F14" s="21">
         <v>60</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G14" s="21">
         <v>50</v>
       </c>
-      <c r="H13" s="20">
+      <c r="H14" s="21">
         <v>39</v>
       </c>
-      <c r="I13" s="20">
+      <c r="I14" s="21">
         <v>30</v>
       </c>
-      <c r="J13" s="20">
+      <c r="J14" s="21">
         <v>20</v>
       </c>
-      <c r="K13" s="20">
+      <c r="K14" s="21">
         <v>10</v>
       </c>
-      <c r="L13" s="20">
+      <c r="L14" s="21">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="19">
+    <row r="15" spans="1:12">
+      <c r="A15" s="22">
         <v>46105</v>
       </c>
-      <c r="B14" s="20">
+      <c r="B15" s="21">
         <v>97</v>
       </c>
-      <c r="C14" s="20">
+      <c r="C15" s="21">
         <v>87</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D15" s="21">
         <v>78</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E15" s="21">
         <v>67</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F15" s="21">
         <v>58</v>
       </c>
-      <c r="G14" s="20">
+      <c r="G15" s="21">
         <v>49</v>
       </c>
-      <c r="H14" s="20">
+      <c r="H15" s="21">
         <v>38</v>
       </c>
-      <c r="I14" s="20">
+      <c r="I15" s="21">
         <v>29</v>
       </c>
-      <c r="J14" s="20">
+      <c r="J15" s="21">
         <v>19</v>
       </c>
-      <c r="K14" s="20">
+      <c r="K15" s="21">
         <v>9</v>
       </c>
-      <c r="L14" s="20">
+      <c r="L15" s="21">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="19">
+    <row r="16" spans="1:12">
+      <c r="A16" s="22">
         <v>46108</v>
       </c>
-      <c r="B15" s="20">
+      <c r="B16" s="21">
         <v>102</v>
       </c>
-      <c r="C15" s="20">
+      <c r="C16" s="21">
         <v>94</v>
       </c>
-      <c r="D15" s="20">
+      <c r="D16" s="21">
         <v>84</v>
       </c>
-      <c r="E15" s="20">
+      <c r="E16" s="21">
         <v>74</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F16" s="21">
         <v>64</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G16" s="21">
         <v>55</v>
       </c>
-      <c r="H15" s="20">
+      <c r="H16" s="21">
         <v>44</v>
       </c>
-      <c r="I15" s="20">
+      <c r="I16" s="21">
         <v>34</v>
       </c>
-      <c r="J15" s="20">
+      <c r="J16" s="21">
         <v>23</v>
       </c>
-      <c r="K15" s="20">
+      <c r="K16" s="21">
         <v>11</v>
       </c>
-      <c r="L15" s="20">
+      <c r="L16" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="23">
+        <v>46112</v>
+      </c>
+      <c r="B17" s="14">
+        <v>98</v>
+      </c>
+      <c r="C17" s="14">
+        <v>88</v>
+      </c>
+      <c r="D17" s="14">
+        <v>77</v>
+      </c>
+      <c r="E17" s="14">
+        <v>67</v>
+      </c>
+      <c r="F17" s="14">
+        <v>59</v>
+      </c>
+      <c r="G17" s="14">
+        <v>49</v>
+      </c>
+      <c r="H17" s="14">
+        <v>38</v>
+      </c>
+      <c r="I17" s="14">
+        <v>29</v>
+      </c>
+      <c r="J17" s="14">
+        <v>19</v>
+      </c>
+      <c r="K17" s="14">
+        <v>10</v>
+      </c>
+      <c r="L17" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B18" s="21">
+        <f>AVERAGE(B13:B17)</f>
+        <v>98.6</v>
+      </c>
+      <c r="C18" s="21">
+        <f t="shared" ref="C18:L18" si="2">AVERAGE(C13:C17)</f>
+        <v>89</v>
+      </c>
+      <c r="D18" s="21">
+        <f t="shared" si="2"/>
+        <v>79</v>
+      </c>
+      <c r="E18" s="21">
+        <f t="shared" si="2"/>
+        <v>68.8</v>
+      </c>
+      <c r="F18" s="21">
+        <f t="shared" si="2"/>
+        <v>59.8</v>
+      </c>
+      <c r="G18" s="21">
+        <f t="shared" si="2"/>
+        <v>50.4</v>
+      </c>
+      <c r="H18" s="21">
+        <f t="shared" si="2"/>
+        <v>39.4</v>
+      </c>
+      <c r="I18" s="21">
+        <f t="shared" si="2"/>
+        <v>30.2</v>
+      </c>
+      <c r="J18" s="21">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="K18" s="21">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="L18" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="B19" s="24">
+        <f>_xlfn.STDEV.P(B13:B17)</f>
+        <v>1.8547236990991407</v>
+      </c>
+      <c r="C19" s="24">
+        <f t="shared" ref="C19:L19" si="3">_xlfn.STDEV.P(C13:C17)</f>
+        <v>2.6076809620810595</v>
+      </c>
+      <c r="D19" s="24">
+        <f t="shared" si="3"/>
+        <v>2.6076809620810595</v>
+      </c>
+      <c r="E19" s="24">
+        <f t="shared" si="3"/>
+        <v>2.7129319932501073</v>
+      </c>
+      <c r="F19" s="24">
+        <f t="shared" si="3"/>
+        <v>2.2271057451320089</v>
+      </c>
+      <c r="G19" s="24">
+        <f t="shared" si="3"/>
+        <v>2.3323807579381204</v>
+      </c>
+      <c r="H19" s="24">
+        <f t="shared" si="3"/>
+        <v>2.3323807579381204</v>
+      </c>
+      <c r="I19" s="24">
+        <f t="shared" si="3"/>
+        <v>1.9390719429665315</v>
+      </c>
+      <c r="J19" s="24">
+        <f t="shared" si="3"/>
+        <v>1.5491933384829668</v>
+      </c>
+      <c r="K19" s="24">
+        <f t="shared" si="3"/>
+        <v>0.63245553203367588</v>
+      </c>
+      <c r="L19" s="24">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -21624,14 +21910,14 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4"/>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22" t="s">
+      <c r="C1" s="20"/>
+      <c r="D1" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="22"/>
+      <c r="E1" s="20"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4"/>

--- a/results/tables/DisplayBrightness/DisplayBrightness.xlsx
+++ b/results/tables/DisplayBrightness/DisplayBrightness.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HamaKazu\Desktop\GradSchool\lab\experiment\DisplayBrightness\BackgroundDisplay\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HamaKazu\Desktop\GradSchool\lab\results\tables\DisplayBrightness\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86758ED-2D8E-432B-B0F1-35501636AD03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58B05B98-F478-4B94-8A02-26EF3A52301D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FG_RGB_Trance" sheetId="8" r:id="rId1"/>
     <sheet name="FG補正OFF" sheetId="6" r:id="rId2"/>
     <sheet name="FGDisplay" sheetId="2" r:id="rId3"/>
-    <sheet name="BG_RGB_Trance" sheetId="7" r:id="rId4"/>
-    <sheet name="BGDisplay" sheetId="1" r:id="rId5"/>
-    <sheet name="FGLUMI" sheetId="5" r:id="rId6"/>
-    <sheet name="BGLUMI" sheetId="3" r:id="rId7"/>
-    <sheet name="BG補正OFF" sheetId="4" r:id="rId8"/>
+    <sheet name="画素値固定" sheetId="9" r:id="rId4"/>
+    <sheet name="BG_RGB_Trance" sheetId="7" r:id="rId5"/>
+    <sheet name="BGDisplay" sheetId="1" r:id="rId6"/>
+    <sheet name="FGLUMI" sheetId="5" r:id="rId7"/>
+    <sheet name="BGLUMI" sheetId="3" r:id="rId8"/>
+    <sheet name="BG補正OFF" sheetId="4" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="134">
   <si>
     <t>標準光</t>
     <rPh sb="0" eb="2">
@@ -538,14 +539,97 @@
     <t>10'</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>std</t>
+  </si>
+  <si>
+    <t>bg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>fg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 255</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 230</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 217</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 180</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 155</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 102</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 0</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Date</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 254</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 243</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 232</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 202</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 186</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 168</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 148</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 123</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pixel: 90</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="176" formatCode="0.000_ "/>
     <numFmt numFmtId="177" formatCode="0.0_ "/>
+    <numFmt numFmtId="181" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -636,7 +720,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -684,8 +768,23 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -12579,11 +12678,11 @@
         <v>2</v>
       </c>
       <c r="O2">
-        <f t="shared" ref="O2:P2" si="0">ABS(H2-L2)</f>
+        <f>ABS(H2-L2)</f>
         <v>0</v>
       </c>
       <c r="P2">
-        <f t="shared" si="0"/>
+        <f>ABS(I2-M2)</f>
         <v>1</v>
       </c>
       <c r="Q2">
@@ -12591,11 +12690,11 @@
         <v>4</v>
       </c>
       <c r="R2">
-        <f t="shared" ref="R2:S2" si="1">O2^2</f>
+        <f>O2^2</f>
         <v>0</v>
       </c>
       <c r="S2">
-        <f t="shared" si="1"/>
+        <f>P2^2</f>
         <v>1</v>
       </c>
     </row>
@@ -12637,27 +12736,27 @@
         <v>31</v>
       </c>
       <c r="N3">
-        <f t="shared" ref="N3:N11" si="2">ABS(G3-K3)</f>
+        <f t="shared" ref="N3:N11" si="0">ABS(G3-K3)</f>
         <v>1</v>
       </c>
       <c r="O3">
-        <f t="shared" ref="O3:O11" si="3">ABS(H3-L3)</f>
+        <f t="shared" ref="O3:O11" si="1">ABS(H3-L3)</f>
         <v>2</v>
       </c>
       <c r="P3">
-        <f t="shared" ref="P3:P11" si="4">ABS(I3-M3)</f>
+        <f t="shared" ref="P3:P11" si="2">ABS(I3-M3)</f>
         <v>2</v>
       </c>
       <c r="Q3">
-        <f t="shared" ref="Q3:Q11" si="5">N3^2</f>
+        <f t="shared" ref="Q3:Q11" si="3">N3^2</f>
         <v>1</v>
       </c>
       <c r="R3">
-        <f t="shared" ref="R3:R11" si="6">O3^2</f>
+        <f t="shared" ref="R3:R11" si="4">O3^2</f>
         <v>4</v>
       </c>
       <c r="S3">
-        <f t="shared" ref="S3:S11" si="7">P3^2</f>
+        <f t="shared" ref="S3:S11" si="5">P3^2</f>
         <v>4</v>
       </c>
     </row>
@@ -12699,27 +12798,27 @@
         <v>50</v>
       </c>
       <c r="N4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="P4">
         <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="O4">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="P4">
+      <c r="R4">
         <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="Q4">
+        <v>4</v>
+      </c>
+      <c r="S4">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="R4">
-        <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="S4">
-        <f t="shared" si="7"/>
         <v>4</v>
       </c>
     </row>
@@ -12761,27 +12860,27 @@
         <v>34</v>
       </c>
       <c r="N5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P5">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="O5">
+      <c r="Q5">
         <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="P5">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="Q5">
+      <c r="S5">
         <f t="shared" si="5"/>
-        <v>4</v>
-      </c>
-      <c r="R5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <f t="shared" si="7"/>
         <v>4</v>
       </c>
     </row>
@@ -12823,27 +12922,27 @@
         <v>22</v>
       </c>
       <c r="N6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P6">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O6">
+        <v>3</v>
+      </c>
+      <c r="Q6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P6">
+      <c r="R6">
         <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="S6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <f t="shared" si="7"/>
         <v>9</v>
       </c>
     </row>
@@ -12885,27 +12984,27 @@
         <v>17</v>
       </c>
       <c r="N7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P7">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="O7">
+      <c r="Q7">
         <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="P7">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q7">
+      <c r="S7">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="R7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -12935,27 +13034,27 @@
         <v>115</v>
       </c>
       <c r="N8">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="P8">
         <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-      <c r="O8">
+        <v>3</v>
+      </c>
+      <c r="Q8">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="P8">
+        <v>144</v>
+      </c>
+      <c r="R8">
         <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="Q8">
+        <v>4</v>
+      </c>
+      <c r="S8">
         <f t="shared" si="5"/>
-        <v>144</v>
-      </c>
-      <c r="R8">
-        <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="S8">
-        <f t="shared" si="7"/>
         <v>9</v>
       </c>
     </row>
@@ -12994,27 +13093,27 @@
         <v>22</v>
       </c>
       <c r="N9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P9">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
         <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="P9">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q9">
+      <c r="S9">
         <f t="shared" si="5"/>
-        <v>4</v>
-      </c>
-      <c r="R9">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="S9">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -13053,27 +13152,27 @@
         <v>9</v>
       </c>
       <c r="N10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P10">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P10">
+      <c r="R10">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="S10">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -13112,27 +13211,27 @@
         <v>77</v>
       </c>
       <c r="N11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P11">
         <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="O11">
+        <v>2</v>
+      </c>
+      <c r="Q11">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="P11">
+      <c r="R11">
         <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="S11">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="R11">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="S11">
-        <f t="shared" si="7"/>
         <v>4</v>
       </c>
     </row>
@@ -13141,27 +13240,27 @@
         <v>86</v>
       </c>
       <c r="N12">
-        <f>AVERAGE(N2:N11)</f>
+        <f t="shared" ref="N12:S12" si="6">AVERAGE(N2:N11)</f>
         <v>2.2000000000000002</v>
       </c>
       <c r="O12">
-        <f t="shared" ref="O12:S12" si="8">AVERAGE(O2:O11)</f>
+        <f t="shared" si="6"/>
         <v>0.8</v>
       </c>
       <c r="P12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1.7</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="R12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1.4</v>
       </c>
       <c r="S12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>3.7</v>
       </c>
     </row>
@@ -13184,11 +13283,11 @@
         <v>4</v>
       </c>
       <c r="R13">
-        <f t="shared" ref="R13:S13" si="9">SQRT(R12)</f>
+        <f>SQRT(R12)</f>
         <v>1.1832159566199232</v>
       </c>
       <c r="S13">
-        <f t="shared" si="9"/>
+        <f>SQRT(S12)</f>
         <v>1.9235384061671346</v>
       </c>
     </row>
@@ -13346,11 +13445,11 @@
         <v>3</v>
       </c>
       <c r="O18">
-        <f t="shared" ref="O18:O27" si="10">ABS(H18-L18)</f>
+        <f t="shared" ref="O18:O27" si="7">ABS(H18-L18)</f>
         <v>0</v>
       </c>
       <c r="P18">
-        <f t="shared" ref="P18:P27" si="11">ABS(I18-M18)</f>
+        <f t="shared" ref="P18:P27" si="8">ABS(I18-M18)</f>
         <v>0</v>
       </c>
       <c r="Q18">
@@ -13358,11 +13457,11 @@
         <v>9</v>
       </c>
       <c r="R18">
-        <f t="shared" ref="R18:R27" si="12">O18^2</f>
+        <f t="shared" ref="R18:R27" si="9">O18^2</f>
         <v>0</v>
       </c>
       <c r="S18">
-        <f t="shared" ref="S18:S27" si="13">P18^2</f>
+        <f t="shared" ref="S18:S27" si="10">P18^2</f>
         <v>0</v>
       </c>
     </row>
@@ -13404,27 +13503,27 @@
         <v>34</v>
       </c>
       <c r="N19">
-        <f t="shared" ref="N19:N27" si="14">ABS(G19-K19)</f>
+        <f t="shared" ref="N19:N27" si="11">ABS(G19-K19)</f>
         <v>2</v>
       </c>
       <c r="O19">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" ref="Q19:Q27" si="12">N19^2</f>
+        <v>4</v>
+      </c>
+      <c r="R19">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="S19">
         <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-      <c r="P19">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <f t="shared" ref="Q19:Q27" si="15">N19^2</f>
-        <v>4</v>
-      </c>
-      <c r="R19">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-      <c r="S19">
-        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -13454,27 +13553,27 @@
         <v>54</v>
       </c>
       <c r="N20">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="O20">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="R20">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S20">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <f t="shared" si="11"/>
-        <v>2</v>
-      </c>
-      <c r="Q20">
-        <f t="shared" si="15"/>
-        <v>1</v>
-      </c>
-      <c r="R20">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <f t="shared" si="13"/>
         <v>4</v>
       </c>
     </row>
@@ -13507,27 +13606,27 @@
         <v>37</v>
       </c>
       <c r="N21">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
       <c r="O21">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="P21">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="12"/>
+        <v>9</v>
+      </c>
+      <c r="R21">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="S21">
         <f t="shared" si="10"/>
-        <v>2</v>
-      </c>
-      <c r="P21">
-        <f t="shared" si="11"/>
-        <v>2</v>
-      </c>
-      <c r="Q21">
-        <f t="shared" si="15"/>
-        <v>9</v>
-      </c>
-      <c r="R21">
-        <f t="shared" si="12"/>
-        <v>4</v>
-      </c>
-      <c r="S21">
-        <f t="shared" si="13"/>
         <v>4</v>
       </c>
     </row>
@@ -13560,27 +13659,27 @@
         <v>24</v>
       </c>
       <c r="N22">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="O22">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="R22">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S22">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="P22">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <f t="shared" si="15"/>
-        <v>1</v>
-      </c>
-      <c r="R22">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -13613,27 +13712,27 @@
         <v>18</v>
       </c>
       <c r="N23">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="P23">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
+      <c r="O23">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="Q23">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="R23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
+      <c r="R23">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="S23">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -13663,27 +13762,27 @@
         <v>118</v>
       </c>
       <c r="N24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>12</v>
       </c>
       <c r="O24">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="P24">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="Q24">
+        <f t="shared" si="12"/>
+        <v>144</v>
+      </c>
+      <c r="R24">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="S24">
         <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-      <c r="P24">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="Q24">
-        <f t="shared" si="15"/>
-        <v>144</v>
-      </c>
-      <c r="R24">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-      <c r="S24">
-        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -13713,27 +13812,27 @@
         <v>21</v>
       </c>
       <c r="N25">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="O25">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="P25">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
+      <c r="O25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
       <c r="Q25">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="R25">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -13763,27 +13862,27 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="P26">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="Q26">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="R26">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
+      <c r="R26">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="S26">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -13813,53 +13912,53 @@
         <v>81</v>
       </c>
       <c r="N27">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="O27">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="P27">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
+      <c r="O27">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
       <c r="Q27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="R27">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:19">
       <c r="N28">
-        <f>AVERAGE(N18:N27)</f>
+        <f t="shared" ref="N28:S28" si="13">AVERAGE(N18:N27)</f>
         <v>2.4</v>
       </c>
       <c r="O28">
-        <f t="shared" ref="O28:S28" si="16">AVERAGE(O18:O27)</f>
+        <f t="shared" si="13"/>
         <v>0.4</v>
       </c>
       <c r="P28">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0.8</v>
       </c>
       <c r="Q28">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>17</v>
       </c>
       <c r="R28">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0.6</v>
       </c>
       <c r="S28">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>1.2</v>
       </c>
     </row>
@@ -13873,11 +13972,11 @@
         <v>4.1231056256176606</v>
       </c>
       <c r="R29">
-        <f t="shared" ref="R29:S29" si="17">SQRT(R28)</f>
+        <f>SQRT(R28)</f>
         <v>0.7745966692414834</v>
       </c>
       <c r="S29">
-        <f t="shared" si="17"/>
+        <f>SQRT(S28)</f>
         <v>1.0954451150103321</v>
       </c>
     </row>
@@ -13912,14 +14011,14 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4"/>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19" t="s">
+      <c r="C1" s="20"/>
+      <c r="D1" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="19"/>
+      <c r="E1" s="20"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4"/>
@@ -15517,6 +15616,636 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E63BFBA-8482-4406-A3A3-55ADB73C3469}">
+  <dimension ref="A1:L19"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="19.69921875" customWidth="1"/>
+    <col min="2" max="12" width="14.19921875" style="19" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="22">
+        <v>46098</v>
+      </c>
+      <c r="B3" s="21">
+        <v>30</v>
+      </c>
+      <c r="C3" s="21">
+        <v>25</v>
+      </c>
+      <c r="D3" s="21">
+        <v>19</v>
+      </c>
+      <c r="E3" s="21">
+        <v>15</v>
+      </c>
+      <c r="F3" s="21">
+        <v>9</v>
+      </c>
+      <c r="G3" s="21">
+        <v>6</v>
+      </c>
+      <c r="H3" s="21">
+        <v>0</v>
+      </c>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="22">
+        <v>46103</v>
+      </c>
+      <c r="B4" s="21">
+        <v>30</v>
+      </c>
+      <c r="C4" s="21">
+        <v>26</v>
+      </c>
+      <c r="D4" s="21">
+        <v>20</v>
+      </c>
+      <c r="E4" s="21">
+        <v>16</v>
+      </c>
+      <c r="F4" s="21">
+        <v>9</v>
+      </c>
+      <c r="G4" s="21">
+        <v>6</v>
+      </c>
+      <c r="H4" s="21">
+        <v>0</v>
+      </c>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="22">
+        <v>46105</v>
+      </c>
+      <c r="B5" s="21">
+        <v>29</v>
+      </c>
+      <c r="C5" s="21">
+        <v>25</v>
+      </c>
+      <c r="D5" s="21">
+        <v>19</v>
+      </c>
+      <c r="E5" s="21">
+        <v>16</v>
+      </c>
+      <c r="F5" s="21">
+        <v>9</v>
+      </c>
+      <c r="G5" s="21">
+        <v>6</v>
+      </c>
+      <c r="H5" s="21">
+        <v>0</v>
+      </c>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="21"/>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="22">
+        <v>46108</v>
+      </c>
+      <c r="B6" s="21">
+        <v>31</v>
+      </c>
+      <c r="C6" s="21">
+        <v>27</v>
+      </c>
+      <c r="D6" s="21">
+        <v>21</v>
+      </c>
+      <c r="E6" s="21">
+        <v>17</v>
+      </c>
+      <c r="F6" s="21">
+        <v>11</v>
+      </c>
+      <c r="G6" s="21">
+        <v>7</v>
+      </c>
+      <c r="H6" s="21">
+        <v>0</v>
+      </c>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="21"/>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="23">
+        <v>46112</v>
+      </c>
+      <c r="B7" s="14">
+        <v>29</v>
+      </c>
+      <c r="C7" s="14">
+        <v>25</v>
+      </c>
+      <c r="D7" s="14">
+        <v>19</v>
+      </c>
+      <c r="E7" s="14">
+        <v>15</v>
+      </c>
+      <c r="F7" s="14">
+        <v>9</v>
+      </c>
+      <c r="G7" s="14">
+        <v>5</v>
+      </c>
+      <c r="H7" s="14">
+        <v>0</v>
+      </c>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8" s="21">
+        <f>AVERAGE(B3:B7)</f>
+        <v>29.8</v>
+      </c>
+      <c r="C8" s="21">
+        <f t="shared" ref="C8:H8" si="0">AVERAGE(C3:C7)</f>
+        <v>25.6</v>
+      </c>
+      <c r="D8" s="21">
+        <f t="shared" si="0"/>
+        <v>19.600000000000001</v>
+      </c>
+      <c r="E8" s="21">
+        <f t="shared" si="0"/>
+        <v>15.8</v>
+      </c>
+      <c r="F8" s="21">
+        <f t="shared" si="0"/>
+        <v>9.4</v>
+      </c>
+      <c r="G8" s="21">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="H8" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="21"/>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="B9" s="24">
+        <f>_xlfn.STDEV.P(B3:B7)</f>
+        <v>0.74833147735478822</v>
+      </c>
+      <c r="C9" s="24">
+        <f t="shared" ref="C9:H9" si="1">_xlfn.STDEV.P(C3:C7)</f>
+        <v>0.79999999999999993</v>
+      </c>
+      <c r="D9" s="24">
+        <f t="shared" si="1"/>
+        <v>0.79999999999999993</v>
+      </c>
+      <c r="E9" s="24">
+        <f t="shared" si="1"/>
+        <v>0.74833147735478822</v>
+      </c>
+      <c r="F9" s="24">
+        <f t="shared" si="1"/>
+        <v>0.79999999999999993</v>
+      </c>
+      <c r="G9" s="24">
+        <f t="shared" si="1"/>
+        <v>0.63245553203367588</v>
+      </c>
+      <c r="H9" s="24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="21"/>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="21"/>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="21"/>
+      <c r="L11" s="21"/>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="I12" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="22">
+        <v>46098</v>
+      </c>
+      <c r="B13" s="21">
+        <v>97</v>
+      </c>
+      <c r="C13" s="21">
+        <v>87</v>
+      </c>
+      <c r="D13" s="21">
+        <v>77</v>
+      </c>
+      <c r="E13" s="21">
+        <v>67</v>
+      </c>
+      <c r="F13" s="21">
+        <v>58</v>
+      </c>
+      <c r="G13" s="21">
+        <v>49</v>
+      </c>
+      <c r="H13" s="21">
+        <v>38</v>
+      </c>
+      <c r="I13" s="21">
+        <v>29</v>
+      </c>
+      <c r="J13" s="21">
+        <v>19</v>
+      </c>
+      <c r="K13" s="21">
+        <v>10</v>
+      </c>
+      <c r="L13" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="22">
+        <v>46103</v>
+      </c>
+      <c r="B14" s="21">
+        <v>99</v>
+      </c>
+      <c r="C14" s="21">
+        <v>89</v>
+      </c>
+      <c r="D14" s="21">
+        <v>79</v>
+      </c>
+      <c r="E14" s="21">
+        <v>69</v>
+      </c>
+      <c r="F14" s="21">
+        <v>60</v>
+      </c>
+      <c r="G14" s="21">
+        <v>50</v>
+      </c>
+      <c r="H14" s="21">
+        <v>39</v>
+      </c>
+      <c r="I14" s="21">
+        <v>30</v>
+      </c>
+      <c r="J14" s="21">
+        <v>20</v>
+      </c>
+      <c r="K14" s="21">
+        <v>10</v>
+      </c>
+      <c r="L14" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="22">
+        <v>46105</v>
+      </c>
+      <c r="B15" s="21">
+        <v>97</v>
+      </c>
+      <c r="C15" s="21">
+        <v>87</v>
+      </c>
+      <c r="D15" s="21">
+        <v>78</v>
+      </c>
+      <c r="E15" s="21">
+        <v>67</v>
+      </c>
+      <c r="F15" s="21">
+        <v>58</v>
+      </c>
+      <c r="G15" s="21">
+        <v>49</v>
+      </c>
+      <c r="H15" s="21">
+        <v>38</v>
+      </c>
+      <c r="I15" s="21">
+        <v>29</v>
+      </c>
+      <c r="J15" s="21">
+        <v>19</v>
+      </c>
+      <c r="K15" s="21">
+        <v>9</v>
+      </c>
+      <c r="L15" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="22">
+        <v>46108</v>
+      </c>
+      <c r="B16" s="21">
+        <v>102</v>
+      </c>
+      <c r="C16" s="21">
+        <v>94</v>
+      </c>
+      <c r="D16" s="21">
+        <v>84</v>
+      </c>
+      <c r="E16" s="21">
+        <v>74</v>
+      </c>
+      <c r="F16" s="21">
+        <v>64</v>
+      </c>
+      <c r="G16" s="21">
+        <v>55</v>
+      </c>
+      <c r="H16" s="21">
+        <v>44</v>
+      </c>
+      <c r="I16" s="21">
+        <v>34</v>
+      </c>
+      <c r="J16" s="21">
+        <v>23</v>
+      </c>
+      <c r="K16" s="21">
+        <v>11</v>
+      </c>
+      <c r="L16" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="23">
+        <v>46112</v>
+      </c>
+      <c r="B17" s="14">
+        <v>98</v>
+      </c>
+      <c r="C17" s="14">
+        <v>88</v>
+      </c>
+      <c r="D17" s="14">
+        <v>77</v>
+      </c>
+      <c r="E17" s="14">
+        <v>67</v>
+      </c>
+      <c r="F17" s="14">
+        <v>59</v>
+      </c>
+      <c r="G17" s="14">
+        <v>49</v>
+      </c>
+      <c r="H17" s="14">
+        <v>38</v>
+      </c>
+      <c r="I17" s="14">
+        <v>29</v>
+      </c>
+      <c r="J17" s="14">
+        <v>19</v>
+      </c>
+      <c r="K17" s="14">
+        <v>10</v>
+      </c>
+      <c r="L17" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B18" s="21">
+        <f>AVERAGE(B13:B17)</f>
+        <v>98.6</v>
+      </c>
+      <c r="C18" s="21">
+        <f t="shared" ref="C18:L18" si="2">AVERAGE(C13:C17)</f>
+        <v>89</v>
+      </c>
+      <c r="D18" s="21">
+        <f t="shared" si="2"/>
+        <v>79</v>
+      </c>
+      <c r="E18" s="21">
+        <f t="shared" si="2"/>
+        <v>68.8</v>
+      </c>
+      <c r="F18" s="21">
+        <f t="shared" si="2"/>
+        <v>59.8</v>
+      </c>
+      <c r="G18" s="21">
+        <f t="shared" si="2"/>
+        <v>50.4</v>
+      </c>
+      <c r="H18" s="21">
+        <f t="shared" si="2"/>
+        <v>39.4</v>
+      </c>
+      <c r="I18" s="21">
+        <f t="shared" si="2"/>
+        <v>30.2</v>
+      </c>
+      <c r="J18" s="21">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="K18" s="21">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="L18" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="B19" s="24">
+        <f>_xlfn.STDEV.P(B13:B17)</f>
+        <v>1.8547236990991407</v>
+      </c>
+      <c r="C19" s="24">
+        <f t="shared" ref="C19:L19" si="3">_xlfn.STDEV.P(C13:C17)</f>
+        <v>2.6076809620810595</v>
+      </c>
+      <c r="D19" s="24">
+        <f t="shared" si="3"/>
+        <v>2.6076809620810595</v>
+      </c>
+      <c r="E19" s="24">
+        <f t="shared" si="3"/>
+        <v>2.7129319932501073</v>
+      </c>
+      <c r="F19" s="24">
+        <f t="shared" si="3"/>
+        <v>2.2271057451320089</v>
+      </c>
+      <c r="G19" s="24">
+        <f t="shared" si="3"/>
+        <v>2.3323807579381204</v>
+      </c>
+      <c r="H19" s="24">
+        <f t="shared" si="3"/>
+        <v>2.3323807579381204</v>
+      </c>
+      <c r="I19" s="24">
+        <f t="shared" si="3"/>
+        <v>1.9390719429665315</v>
+      </c>
+      <c r="J19" s="24">
+        <f t="shared" si="3"/>
+        <v>1.5491933384829668</v>
+      </c>
+      <c r="K19" s="24">
+        <f t="shared" si="3"/>
+        <v>0.63245553203367588</v>
+      </c>
+      <c r="L19" s="24">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50473ED6-92DB-49CB-BB73-3D59C4C4199E}">
   <dimension ref="A1:S31"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -15617,11 +16346,11 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <f t="shared" ref="O2:P2" si="0">ABS(H2-L2)</f>
+        <f>ABS(H2-L2)</f>
         <v>1</v>
       </c>
       <c r="P2">
-        <f t="shared" si="0"/>
+        <f>ABS(I2-M2)</f>
         <v>0</v>
       </c>
       <c r="Q2">
@@ -15629,11 +16358,11 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <f t="shared" ref="R2:S11" si="1">O2^2</f>
+        <f t="shared" ref="R2:S11" si="0">O2^2</f>
         <v>1</v>
       </c>
       <c r="S2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -15675,27 +16404,27 @@
         <v>17</v>
       </c>
       <c r="N3">
-        <f t="shared" ref="N3:N11" si="2">ABS(G3-K3)</f>
+        <f t="shared" ref="N3:N11" si="1">ABS(G3-K3)</f>
         <v>2</v>
       </c>
       <c r="O3">
-        <f t="shared" ref="O3:O11" si="3">ABS(H3-L3)</f>
+        <f t="shared" ref="O3:O11" si="2">ABS(H3-L3)</f>
         <v>2</v>
       </c>
       <c r="P3">
-        <f t="shared" ref="P3:P11" si="4">ABS(I3-M3)</f>
+        <f t="shared" ref="P3:P11" si="3">ABS(I3-M3)</f>
         <v>0</v>
       </c>
       <c r="Q3">
-        <f t="shared" ref="Q3:Q11" si="5">N3^2</f>
+        <f t="shared" ref="Q3:Q11" si="4">N3^2</f>
         <v>4</v>
       </c>
       <c r="R3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="S3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -15737,27 +16466,27 @@
         <v>29</v>
       </c>
       <c r="N4">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="O4">
         <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="O4">
+        <v>4</v>
+      </c>
+      <c r="P4">
         <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q4">
-        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="R4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="S4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -15799,27 +16528,27 @@
         <v>18</v>
       </c>
       <c r="N5">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="O5">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="O5">
+        <v>2</v>
+      </c>
+      <c r="P5">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="R5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="S5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -15861,27 +16590,27 @@
         <v>13</v>
       </c>
       <c r="N6">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="O6">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q6">
-        <f t="shared" si="5"/>
-        <v>4</v>
-      </c>
-      <c r="R6">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="S6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -15923,27 +16652,27 @@
         <v>11</v>
       </c>
       <c r="N7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="O7">
         <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="O7">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="P7">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="Q7">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
       <c r="R7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="S7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -15973,27 +16702,27 @@
         <v>69</v>
       </c>
       <c r="N8">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="O8">
         <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
-      <c r="O8">
+        <v>4</v>
+      </c>
+      <c r="P8">
         <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q8">
-        <f t="shared" si="5"/>
         <v>196</v>
       </c>
       <c r="R8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="S8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -16032,27 +16761,27 @@
         <v>15</v>
       </c>
       <c r="N9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O9">
         <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O9">
-        <f t="shared" si="3"/>
+      <c r="R9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="P9">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="Q9">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="S9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -16091,27 +16820,27 @@
         <v>7</v>
       </c>
       <c r="N10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="O10">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q10">
-        <f t="shared" si="5"/>
-        <v>9</v>
-      </c>
-      <c r="R10">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="S10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -16150,27 +16879,27 @@
         <v>44</v>
       </c>
       <c r="N11">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="O11">
         <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="O11">
+        <v>4</v>
+      </c>
+      <c r="P11">
         <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="R11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="S11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -16179,27 +16908,27 @@
         <v>86</v>
       </c>
       <c r="N12">
-        <f>AVERAGE(N2:N11)</f>
+        <f t="shared" ref="N12:S12" si="5">AVERAGE(N2:N11)</f>
         <v>3.5</v>
       </c>
       <c r="O12">
-        <f t="shared" ref="O12:P12" si="6">AVERAGE(O2:O11)</f>
+        <f t="shared" si="5"/>
         <v>2.2999999999999998</v>
       </c>
       <c r="P12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.8</v>
       </c>
       <c r="Q12">
-        <f t="shared" ref="Q12" si="7">AVERAGE(Q2:Q11)</f>
+        <f t="shared" si="5"/>
         <v>27.3</v>
       </c>
       <c r="R12">
-        <f t="shared" ref="R12" si="8">AVERAGE(R2:R11)</f>
+        <f t="shared" si="5"/>
         <v>6.9</v>
       </c>
       <c r="S12">
-        <f t="shared" ref="S12" si="9">AVERAGE(S2:S11)</f>
+        <f t="shared" si="5"/>
         <v>1.2</v>
       </c>
     </row>
@@ -16222,11 +16951,11 @@
         <v>5.2249401910452526</v>
       </c>
       <c r="R13">
-        <f t="shared" ref="R13:S13" si="10">SQRT(R12)</f>
+        <f>SQRT(R12)</f>
         <v>2.6267851073127395</v>
       </c>
       <c r="S13">
-        <f t="shared" si="10"/>
+        <f>SQRT(S12)</f>
         <v>1.0954451150103321</v>
       </c>
     </row>
@@ -16384,11 +17113,11 @@
         <v>0</v>
       </c>
       <c r="O18">
-        <f t="shared" ref="O18:O27" si="11">ABS(H18-L18)</f>
+        <f t="shared" ref="O18:O27" si="6">ABS(H18-L18)</f>
         <v>0</v>
       </c>
       <c r="P18">
-        <f t="shared" ref="P18:P27" si="12">ABS(I18-M18)</f>
+        <f t="shared" ref="P18:P27" si="7">ABS(I18-M18)</f>
         <v>1</v>
       </c>
       <c r="Q18">
@@ -16396,11 +17125,11 @@
         <v>0</v>
       </c>
       <c r="R18">
-        <f t="shared" ref="R18:R27" si="13">O18^2</f>
+        <f t="shared" ref="R18:R27" si="8">O18^2</f>
         <v>0</v>
       </c>
       <c r="S18">
-        <f t="shared" ref="S18:S27" si="14">P18^2</f>
+        <f t="shared" ref="S18:S27" si="9">P18^2</f>
         <v>1</v>
       </c>
     </row>
@@ -16442,27 +17171,27 @@
         <v>17</v>
       </c>
       <c r="N19">
-        <f t="shared" ref="N19:N27" si="15">ABS(G19-K19)</f>
+        <f t="shared" ref="N19:N27" si="10">ABS(G19-K19)</f>
         <v>1</v>
       </c>
       <c r="O19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="P19">
-        <f t="shared" si="12"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q19">
-        <f t="shared" ref="Q19:Q27" si="16">N19^2</f>
+        <f t="shared" ref="Q19:Q27" si="11">N19^2</f>
         <v>1</v>
       </c>
       <c r="R19">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
       <c r="S19">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -16492,27 +17221,27 @@
         <v>29</v>
       </c>
       <c r="N20">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
       <c r="O20">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="P20">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q20">
         <f t="shared" si="11"/>
-        <v>3</v>
-      </c>
-      <c r="P20">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="Q20">
-        <f t="shared" si="16"/>
         <v>25</v>
       </c>
       <c r="R20">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="S20">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -16542,27 +17271,27 @@
         <v>18</v>
       </c>
       <c r="N21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="O21">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="P21">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="Q21">
         <f t="shared" si="11"/>
-        <v>2</v>
-      </c>
-      <c r="P21">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-      <c r="Q21">
-        <f t="shared" si="16"/>
         <v>16</v>
       </c>
       <c r="R21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
       <c r="S21">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -16592,27 +17321,27 @@
         <v>13</v>
       </c>
       <c r="N22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="O22">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="Q22">
         <f t="shared" si="11"/>
+        <v>4</v>
+      </c>
+      <c r="R22">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="P22">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-      <c r="Q22">
-        <f t="shared" si="16"/>
-        <v>4</v>
-      </c>
-      <c r="R22">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
       <c r="S22">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -16642,27 +17371,27 @@
         <v>11</v>
       </c>
       <c r="N23">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="O23">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="P23">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="Q23">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="P23">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-      <c r="Q23">
-        <f t="shared" si="16"/>
-        <v>4</v>
-      </c>
       <c r="R23">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="S23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -16692,27 +17421,27 @@
         <v>69</v>
       </c>
       <c r="N24">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>12</v>
       </c>
       <c r="O24">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="P24">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="Q24">
         <f t="shared" si="11"/>
-        <v>4</v>
-      </c>
-      <c r="P24">
-        <f t="shared" si="12"/>
-        <v>2</v>
-      </c>
-      <c r="Q24">
-        <f t="shared" si="16"/>
         <v>144</v>
       </c>
       <c r="R24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="S24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
     </row>
@@ -16742,27 +17471,27 @@
         <v>15</v>
       </c>
       <c r="N25">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="O25">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="P25">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="Q25">
         <f t="shared" si="11"/>
-        <v>2</v>
-      </c>
-      <c r="P25">
-        <f t="shared" si="12"/>
-        <v>3</v>
-      </c>
-      <c r="Q25">
-        <f t="shared" si="16"/>
         <v>4</v>
       </c>
       <c r="R25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
       <c r="S25">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
     </row>
@@ -16792,27 +17521,27 @@
         <v>6</v>
       </c>
       <c r="N26">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="O26">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="Q26">
         <f t="shared" si="11"/>
+        <v>4</v>
+      </c>
+      <c r="R26">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="P26">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-      <c r="Q26">
-        <f t="shared" si="16"/>
-        <v>4</v>
-      </c>
-      <c r="R26">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
       <c r="S26">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -16842,53 +17571,53 @@
         <v>44</v>
       </c>
       <c r="N27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
       <c r="O27">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="P27">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q27">
         <f t="shared" si="11"/>
-        <v>5</v>
-      </c>
-      <c r="P27">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="Q27">
-        <f t="shared" si="16"/>
         <v>36</v>
       </c>
       <c r="R27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>25</v>
       </c>
       <c r="S27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:19">
       <c r="N28">
-        <f>AVERAGE(N18:N27)</f>
+        <f t="shared" ref="N28:S28" si="12">AVERAGE(N18:N27)</f>
         <v>3.6</v>
       </c>
       <c r="O28">
-        <f t="shared" ref="O28:S28" si="17">AVERAGE(O18:O27)</f>
+        <f t="shared" si="12"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="P28">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="Q28">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>23.8</v>
       </c>
       <c r="R28">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>7.8</v>
       </c>
       <c r="S28">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>1.8</v>
       </c>
     </row>
@@ -16902,11 +17631,11 @@
         <v>4.8785243670601872</v>
       </c>
       <c r="R29">
-        <f t="shared" ref="R29:S29" si="18">SQRT(R28)</f>
+        <f>SQRT(R28)</f>
         <v>2.7928480087537881</v>
       </c>
       <c r="S29">
-        <f t="shared" si="18"/>
+        <f>SQRT(S28)</f>
         <v>1.3416407864998738</v>
       </c>
     </row>
@@ -16934,7 +17663,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q89"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -19017,7 +19746,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{748D88B3-AB89-451F-B4F0-D6322845623C}">
   <dimension ref="A1:AF20"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -20043,7 +20772,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4F1D99B-35E9-4F54-9502-3DA711A1E317}">
   <dimension ref="A1:AF25"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -21174,21 +21903,21 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F91A220-ECA8-426C-9CB4-6411C694E3C1}">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4"/>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19" t="s">
+      <c r="C1" s="20"/>
+      <c r="D1" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="19"/>
+      <c r="E1" s="20"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4"/>

--- a/results/tables/DisplayBrightness/DisplayBrightness.xlsx
+++ b/results/tables/DisplayBrightness/DisplayBrightness.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HamaKazu\Desktop\GradSchool\lab\results\tables\DisplayBrightness\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58B05B98-F478-4B94-8A02-26EF3A52301D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{875BAD69-A19F-4217-B727-715126A79504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FG_RGB_Trance" sheetId="8" r:id="rId1"/>
@@ -629,9 +629,9 @@
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="0.000_ "/>
     <numFmt numFmtId="177" formatCode="0.0_ "/>
-    <numFmt numFmtId="181" formatCode="0.00_ "/>
+    <numFmt numFmtId="178" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -645,6 +645,12 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -720,7 +726,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -771,9 +777,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -783,8 +786,14 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -12583,10 +12592,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E41A2DC-6B17-4D94-85B7-1414CA46C384}">
-  <dimension ref="A1:S31"/>
+  <dimension ref="A1:W31"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:23">
       <c r="B1" t="s">
         <v>67</v>
       </c>
@@ -12636,7 +12645,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:23">
       <c r="A2" t="s">
         <v>67</v>
       </c>
@@ -12697,8 +12706,17 @@
         <f>P2^2</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:19">
+      <c r="U2" s="25">
+        <v>0.91309865000000001</v>
+      </c>
+      <c r="V2">
+        <v>2.0288560000000001E-2</v>
+      </c>
+      <c r="W2">
+        <v>2.9556829999999999E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23">
       <c r="A3" t="s">
         <v>68</v>
       </c>
@@ -12759,8 +12777,17 @@
         <f t="shared" ref="S3:S11" si="5">P3^2</f>
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:19">
+      <c r="U3" s="25">
+        <v>5.7805429999999998E-2</v>
+      </c>
+      <c r="V3">
+        <v>0.84687323000000003</v>
+      </c>
+      <c r="W3">
+        <v>0.14995979000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23">
       <c r="A4" t="s">
         <v>69</v>
       </c>
@@ -12821,8 +12848,17 @@
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:19">
+      <c r="U4" s="25">
+        <v>2.1246899999999998E-3</v>
+      </c>
+      <c r="V4">
+        <v>2.732089E-2</v>
+      </c>
+      <c r="W4">
+        <v>0.73791041000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23">
       <c r="A5" t="s">
         <v>70</v>
       </c>
@@ -12883,8 +12919,17 @@
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:19">
+      <c r="U5" s="25">
+        <v>0.25015828000000001</v>
+      </c>
+      <c r="V5">
+        <v>8.0231899999999995E-3</v>
+      </c>
+      <c r="W5">
+        <v>3.3465399999999998E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23">
       <c r="A6" t="s">
         <v>71</v>
       </c>
@@ -12945,8 +12990,17 @@
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:19">
+      <c r="U6" s="25">
+        <v>1.680738E-2</v>
+      </c>
+      <c r="V6">
+        <v>0.21223075999999999</v>
+      </c>
+      <c r="W6">
+        <v>3.9546240000000003E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23">
       <c r="A7" t="s">
         <v>72</v>
       </c>
@@ -13007,8 +13061,17 @@
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:19">
+      <c r="U7" s="25">
+        <v>2.1246899999999998E-3</v>
+      </c>
+      <c r="V7">
+        <v>9.1340599999999994E-3</v>
+      </c>
+      <c r="W7">
+        <v>0.15896083999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23">
       <c r="F8">
         <v>7</v>
       </c>
@@ -13057,8 +13120,20 @@
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:19">
+      <c r="U8">
+        <f>U5/U2</f>
+        <v>0.27396632335399906</v>
+      </c>
+      <c r="V8">
+        <f t="shared" ref="V8:W8" si="6">V5/V2</f>
+        <v>0.39545389125694475</v>
+      </c>
+      <c r="W8">
+        <f t="shared" si="6"/>
+        <v>0.11322391474322517</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23">
       <c r="B9">
         <v>0.55900000000000005</v>
       </c>
@@ -13116,8 +13191,20 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:19">
+      <c r="U9">
+        <f t="shared" ref="U9:W9" si="7">U6/U3</f>
+        <v>0.29075780597082318</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="7"/>
+        <v>0.25060511122780438</v>
+      </c>
+      <c r="W9">
+        <f t="shared" si="7"/>
+        <v>0.26371229247520284</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23">
       <c r="B10">
         <v>2.3999999999999998E-3</v>
       </c>
@@ -13175,8 +13262,20 @@
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:19">
+      <c r="U10">
+        <f t="shared" ref="U10:W10" si="8">U7/U4</f>
+        <v>1</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="8"/>
+        <v>0.33432512630445055</v>
+      </c>
+      <c r="W10">
+        <f t="shared" si="8"/>
+        <v>0.21542024322437731</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23">
       <c r="B11">
         <v>6.9999999999999999E-4</v>
       </c>
@@ -13235,36 +13334,36 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:23">
       <c r="A12" t="s">
         <v>86</v>
       </c>
       <c r="N12">
-        <f t="shared" ref="N12:S12" si="6">AVERAGE(N2:N11)</f>
+        <f t="shared" ref="N12:S12" si="9">AVERAGE(N2:N11)</f>
         <v>2.2000000000000002</v>
       </c>
       <c r="O12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0.8</v>
       </c>
       <c r="P12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1.7</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>16</v>
       </c>
       <c r="R12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1.4</v>
       </c>
       <c r="S12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>3.7</v>
       </c>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:23">
       <c r="B13" t="s">
         <v>67</v>
       </c>
@@ -13291,7 +13390,7 @@
         <v>1.9235384061671346</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:23">
       <c r="A14" t="s">
         <v>67</v>
       </c>
@@ -13316,7 +13415,7 @@
         <v>2.6520432374554779</v>
       </c>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:23">
       <c r="A15" t="s">
         <v>68</v>
       </c>
@@ -13333,7 +13432,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:23">
       <c r="A16" t="s">
         <v>69</v>
       </c>
@@ -13445,11 +13544,11 @@
         <v>3</v>
       </c>
       <c r="O18">
-        <f t="shared" ref="O18:O27" si="7">ABS(H18-L18)</f>
+        <f t="shared" ref="O18:O27" si="10">ABS(H18-L18)</f>
         <v>0</v>
       </c>
       <c r="P18">
-        <f t="shared" ref="P18:P27" si="8">ABS(I18-M18)</f>
+        <f t="shared" ref="P18:P27" si="11">ABS(I18-M18)</f>
         <v>0</v>
       </c>
       <c r="Q18">
@@ -13457,11 +13556,11 @@
         <v>9</v>
       </c>
       <c r="R18">
-        <f t="shared" ref="R18:R27" si="9">O18^2</f>
+        <f t="shared" ref="R18:R27" si="12">O18^2</f>
         <v>0</v>
       </c>
       <c r="S18">
-        <f t="shared" ref="S18:S27" si="10">P18^2</f>
+        <f t="shared" ref="S18:S27" si="13">P18^2</f>
         <v>0</v>
       </c>
     </row>
@@ -13503,27 +13602,27 @@
         <v>34</v>
       </c>
       <c r="N19">
-        <f t="shared" ref="N19:N27" si="11">ABS(G19-K19)</f>
+        <f t="shared" ref="N19:N27" si="14">ABS(G19-K19)</f>
         <v>2</v>
       </c>
       <c r="O19">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="P19">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q19">
-        <f t="shared" ref="Q19:Q27" si="12">N19^2</f>
+        <f t="shared" ref="Q19:Q27" si="15">N19^2</f>
         <v>4</v>
       </c>
       <c r="R19">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="S19">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -13553,27 +13652,27 @@
         <v>54</v>
       </c>
       <c r="N20">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P20">
         <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="O20">
-        <f t="shared" si="7"/>
+      <c r="R20">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="P20">
-        <f t="shared" si="8"/>
-        <v>2</v>
-      </c>
-      <c r="Q20">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-      <c r="R20">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
       <c r="S20">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>4</v>
       </c>
     </row>
@@ -13606,27 +13705,27 @@
         <v>37</v>
       </c>
       <c r="N21">
+        <f t="shared" si="14"/>
+        <v>3</v>
+      </c>
+      <c r="O21">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="P21">
         <f t="shared" si="11"/>
-        <v>3</v>
-      </c>
-      <c r="O21">
-        <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="P21">
-        <f t="shared" si="8"/>
-        <v>2</v>
-      </c>
       <c r="Q21">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="R21">
         <f t="shared" si="12"/>
-        <v>9</v>
-      </c>
-      <c r="R21">
-        <f t="shared" si="9"/>
         <v>4</v>
       </c>
       <c r="S21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>4</v>
       </c>
     </row>
@@ -13659,27 +13758,27 @@
         <v>24</v>
       </c>
       <c r="N22">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="O22">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P22">
         <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="O22">
-        <f t="shared" si="7"/>
+      <c r="R22">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="P22">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-      <c r="R22">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
       <c r="S22">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -13712,27 +13811,27 @@
         <v>18</v>
       </c>
       <c r="N23">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P23">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="O23">
-        <f t="shared" si="7"/>
+      <c r="Q23">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="P23">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="Q23">
+      <c r="R23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="R23">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
       <c r="S23">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -13762,27 +13861,27 @@
         <v>118</v>
       </c>
       <c r="N24">
+        <f t="shared" si="14"/>
+        <v>12</v>
+      </c>
+      <c r="O24">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="P24">
         <f t="shared" si="11"/>
-        <v>12</v>
-      </c>
-      <c r="O24">
-        <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="P24">
-        <f t="shared" si="8"/>
+      <c r="Q24">
+        <f t="shared" si="15"/>
+        <v>144</v>
+      </c>
+      <c r="R24">
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="Q24">
-        <f t="shared" si="12"/>
-        <v>144</v>
-      </c>
-      <c r="R24">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
       <c r="S24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -13812,27 +13911,27 @@
         <v>21</v>
       </c>
       <c r="N25">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="O25">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P25">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="O25">
-        <f t="shared" si="7"/>
+      <c r="Q25">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="R25">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="P25">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="Q25">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-      <c r="R25">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
       <c r="S25">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -13862,27 +13961,27 @@
         <v>10</v>
       </c>
       <c r="N26">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P26">
         <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="Q26">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="O26">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="P26">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="Q26">
+      <c r="R26">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="R26">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
       <c r="S26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -13912,53 +14011,53 @@
         <v>81</v>
       </c>
       <c r="N27">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="O27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P27">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="O27">
-        <f t="shared" si="7"/>
+      <c r="Q27">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="R27">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="P27">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="Q27">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-      <c r="R27">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
       <c r="S27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:19">
       <c r="N28">
-        <f t="shared" ref="N28:S28" si="13">AVERAGE(N18:N27)</f>
+        <f t="shared" ref="N28:S28" si="16">AVERAGE(N18:N27)</f>
         <v>2.4</v>
       </c>
       <c r="O28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0.4</v>
       </c>
       <c r="P28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0.8</v>
       </c>
       <c r="Q28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>17</v>
       </c>
       <c r="R28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0.6</v>
       </c>
       <c r="S28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1.2</v>
       </c>
     </row>
@@ -14011,14 +14110,14 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4"/>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20" t="s">
+      <c r="C1" s="24"/>
+      <c r="D1" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="20"/>
+      <c r="E1" s="24"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4"/>
@@ -15654,133 +15753,133 @@
       <c r="H2" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="22">
+      <c r="A3" s="21">
         <v>46098</v>
       </c>
-      <c r="B3" s="21">
+      <c r="B3" s="20">
         <v>30</v>
       </c>
-      <c r="C3" s="21">
+      <c r="C3" s="20">
         <v>25</v>
       </c>
-      <c r="D3" s="21">
+      <c r="D3" s="20">
         <v>19</v>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="20">
         <v>15</v>
       </c>
-      <c r="F3" s="21">
+      <c r="F3" s="20">
         <v>9</v>
       </c>
-      <c r="G3" s="21">
+      <c r="G3" s="20">
         <v>6</v>
       </c>
-      <c r="H3" s="21">
+      <c r="H3" s="20">
         <v>0</v>
       </c>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
-      <c r="L3" s="21"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="22">
+      <c r="A4" s="21">
         <v>46103</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="20">
         <v>30</v>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="20">
         <v>26</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="20">
         <v>20</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="20">
         <v>16</v>
       </c>
-      <c r="F4" s="21">
+      <c r="F4" s="20">
         <v>9</v>
       </c>
-      <c r="G4" s="21">
+      <c r="G4" s="20">
         <v>6</v>
       </c>
-      <c r="H4" s="21">
+      <c r="H4" s="20">
         <v>0</v>
       </c>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="22">
+      <c r="A5" s="21">
         <v>46105</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="20">
         <v>29</v>
       </c>
-      <c r="C5" s="21">
+      <c r="C5" s="20">
         <v>25</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="20">
         <v>19</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="20">
         <v>16</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="20">
         <v>9</v>
       </c>
-      <c r="G5" s="21">
+      <c r="G5" s="20">
         <v>6</v>
       </c>
-      <c r="H5" s="21">
+      <c r="H5" s="20">
         <v>0</v>
       </c>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="22">
+      <c r="A6" s="21">
         <v>46108</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="20">
         <v>31</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="20">
         <v>27</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="20">
         <v>21</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="20">
         <v>17</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="20">
         <v>11</v>
       </c>
-      <c r="G6" s="21">
+      <c r="G6" s="20">
         <v>7</v>
       </c>
-      <c r="H6" s="21">
+      <c r="H6" s="20">
         <v>0</v>
       </c>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="21"/>
-      <c r="L6" s="21"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="23">
+      <c r="A7" s="22">
         <v>46112</v>
       </c>
       <c r="B7" s="14">
@@ -15804,114 +15903,114 @@
       <c r="H7" s="14">
         <v>0</v>
       </c>
-      <c r="I7" s="21"/>
-      <c r="J7" s="21"/>
-      <c r="K7" s="21"/>
-      <c r="L7" s="21"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="20">
         <f>AVERAGE(B3:B7)</f>
         <v>29.8</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="20">
         <f t="shared" ref="C8:H8" si="0">AVERAGE(C3:C7)</f>
         <v>25.6</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="20">
         <f t="shared" si="0"/>
         <v>19.600000000000001</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="20">
         <f t="shared" si="0"/>
         <v>15.8</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="20">
         <f t="shared" si="0"/>
         <v>9.4</v>
       </c>
-      <c r="G8" s="21">
+      <c r="G8" s="20">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="H8" s="21">
+      <c r="H8" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I8" s="21"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="21"/>
-      <c r="L8" s="21"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="23">
         <f>_xlfn.STDEV.P(B3:B7)</f>
         <v>0.74833147735478822</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="23">
         <f t="shared" ref="C9:H9" si="1">_xlfn.STDEV.P(C3:C7)</f>
         <v>0.79999999999999993</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="23">
         <f t="shared" si="1"/>
         <v>0.79999999999999993</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="23">
         <f t="shared" si="1"/>
         <v>0.74833147735478822</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="23">
         <f t="shared" si="1"/>
         <v>0.79999999999999993</v>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="23">
         <f t="shared" si="1"/>
         <v>0.63245553203367588</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="21"/>
-      <c r="L9" s="21"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="21"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="21"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="16" t="s">
@@ -15952,159 +16051,159 @@
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="22">
+      <c r="A13" s="21">
         <v>46098</v>
       </c>
-      <c r="B13" s="21">
+      <c r="B13" s="20">
         <v>97</v>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="20">
         <v>87</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="20">
         <v>77</v>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="20">
         <v>67</v>
       </c>
-      <c r="F13" s="21">
+      <c r="F13" s="20">
         <v>58</v>
       </c>
-      <c r="G13" s="21">
+      <c r="G13" s="20">
         <v>49</v>
       </c>
-      <c r="H13" s="21">
+      <c r="H13" s="20">
         <v>38</v>
       </c>
-      <c r="I13" s="21">
+      <c r="I13" s="20">
         <v>29</v>
       </c>
-      <c r="J13" s="21">
+      <c r="J13" s="20">
         <v>19</v>
       </c>
-      <c r="K13" s="21">
+      <c r="K13" s="20">
         <v>10</v>
       </c>
-      <c r="L13" s="21">
+      <c r="L13" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="22">
+      <c r="A14" s="21">
         <v>46103</v>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="20">
         <v>99</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="20">
         <v>89</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="20">
         <v>79</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="20">
         <v>69</v>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="20">
         <v>60</v>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="20">
         <v>50</v>
       </c>
-      <c r="H14" s="21">
+      <c r="H14" s="20">
         <v>39</v>
       </c>
-      <c r="I14" s="21">
+      <c r="I14" s="20">
         <v>30</v>
       </c>
-      <c r="J14" s="21">
+      <c r="J14" s="20">
         <v>20</v>
       </c>
-      <c r="K14" s="21">
+      <c r="K14" s="20">
         <v>10</v>
       </c>
-      <c r="L14" s="21">
+      <c r="L14" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="22">
+      <c r="A15" s="21">
         <v>46105</v>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="20">
         <v>97</v>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="20">
         <v>87</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="20">
         <v>78</v>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="20">
         <v>67</v>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="20">
         <v>58</v>
       </c>
-      <c r="G15" s="21">
+      <c r="G15" s="20">
         <v>49</v>
       </c>
-      <c r="H15" s="21">
+      <c r="H15" s="20">
         <v>38</v>
       </c>
-      <c r="I15" s="21">
+      <c r="I15" s="20">
         <v>29</v>
       </c>
-      <c r="J15" s="21">
+      <c r="J15" s="20">
         <v>19</v>
       </c>
-      <c r="K15" s="21">
+      <c r="K15" s="20">
         <v>9</v>
       </c>
-      <c r="L15" s="21">
+      <c r="L15" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="22">
+      <c r="A16" s="21">
         <v>46108</v>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="20">
         <v>102</v>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="20">
         <v>94</v>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="20">
         <v>84</v>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="20">
         <v>74</v>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="20">
         <v>64</v>
       </c>
-      <c r="G16" s="21">
+      <c r="G16" s="20">
         <v>55</v>
       </c>
-      <c r="H16" s="21">
+      <c r="H16" s="20">
         <v>44</v>
       </c>
-      <c r="I16" s="21">
+      <c r="I16" s="20">
         <v>34</v>
       </c>
-      <c r="J16" s="21">
+      <c r="J16" s="20">
         <v>23</v>
       </c>
-      <c r="K16" s="21">
+      <c r="K16" s="20">
         <v>11</v>
       </c>
-      <c r="L16" s="21">
+      <c r="L16" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="23">
+      <c r="A17" s="22">
         <v>46112</v>
       </c>
       <c r="B17" s="14">
@@ -16142,50 +16241,50 @@
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="B18" s="21">
+      <c r="B18" s="20">
         <f>AVERAGE(B13:B17)</f>
         <v>98.6</v>
       </c>
-      <c r="C18" s="21">
+      <c r="C18" s="20">
         <f t="shared" ref="C18:L18" si="2">AVERAGE(C13:C17)</f>
         <v>89</v>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="20">
         <f t="shared" si="2"/>
         <v>79</v>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="20">
         <f t="shared" si="2"/>
         <v>68.8</v>
       </c>
-      <c r="F18" s="21">
+      <c r="F18" s="20">
         <f t="shared" si="2"/>
         <v>59.8</v>
       </c>
-      <c r="G18" s="21">
+      <c r="G18" s="20">
         <f t="shared" si="2"/>
         <v>50.4</v>
       </c>
-      <c r="H18" s="21">
+      <c r="H18" s="20">
         <f t="shared" si="2"/>
         <v>39.4</v>
       </c>
-      <c r="I18" s="21">
+      <c r="I18" s="20">
         <f t="shared" si="2"/>
         <v>30.2</v>
       </c>
-      <c r="J18" s="21">
+      <c r="J18" s="20">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="K18" s="21">
+      <c r="K18" s="20">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="L18" s="21">
+      <c r="L18" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16194,47 +16293,47 @@
       <c r="A19" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="B19" s="24">
+      <c r="B19" s="23">
         <f>_xlfn.STDEV.P(B13:B17)</f>
         <v>1.8547236990991407</v>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="23">
         <f t="shared" ref="C19:L19" si="3">_xlfn.STDEV.P(C13:C17)</f>
         <v>2.6076809620810595</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="23">
         <f t="shared" si="3"/>
         <v>2.6076809620810595</v>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="23">
         <f t="shared" si="3"/>
         <v>2.7129319932501073</v>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="23">
         <f t="shared" si="3"/>
         <v>2.2271057451320089</v>
       </c>
-      <c r="G19" s="24">
+      <c r="G19" s="23">
         <f t="shared" si="3"/>
         <v>2.3323807579381204</v>
       </c>
-      <c r="H19" s="24">
+      <c r="H19" s="23">
         <f t="shared" si="3"/>
         <v>2.3323807579381204</v>
       </c>
-      <c r="I19" s="24">
+      <c r="I19" s="23">
         <f t="shared" si="3"/>
         <v>1.9390719429665315</v>
       </c>
-      <c r="J19" s="24">
+      <c r="J19" s="23">
         <f t="shared" si="3"/>
         <v>1.5491933384829668</v>
       </c>
-      <c r="K19" s="24">
+      <c r="K19" s="23">
         <f t="shared" si="3"/>
         <v>0.63245553203367588</v>
       </c>
-      <c r="L19" s="24">
+      <c r="L19" s="23">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -16247,14 +16346,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50473ED6-92DB-49CB-BB73-3D59C4C4199E}">
-  <dimension ref="A1:S31"/>
+  <dimension ref="A1:W31"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="6" max="6" width="8.796875" style="17"/>
     <col min="10" max="10" width="8.796875" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:23">
       <c r="B1" t="s">
         <v>67</v>
       </c>
@@ -16304,7 +16403,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:23">
       <c r="A2" t="s">
         <v>67</v>
       </c>
@@ -16365,8 +16464,17 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:19">
+      <c r="U2" s="25">
+        <v>0.91309865000000001</v>
+      </c>
+      <c r="V2">
+        <v>2.0288560000000001E-2</v>
+      </c>
+      <c r="W2">
+        <v>1.2286490000000001E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23">
       <c r="A3" t="s">
         <v>68</v>
       </c>
@@ -16427,8 +16535,17 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:19">
+      <c r="U3" s="25">
+        <v>5.4480279999999999E-2</v>
+      </c>
+      <c r="V3">
+        <v>0.83076987999999996</v>
+      </c>
+      <c r="W3">
+        <v>0.13843162000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23">
       <c r="A4" t="s">
         <v>69</v>
       </c>
@@ -16489,8 +16606,17 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:19">
+      <c r="U4" s="25">
+        <v>2.42822E-3</v>
+      </c>
+      <c r="V4">
+        <v>2.121901E-2</v>
+      </c>
+      <c r="W4">
+        <v>0.52099556999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23">
       <c r="A5" t="s">
         <v>70</v>
       </c>
@@ -16551,8 +16677,17 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:19">
+      <c r="U5" s="25">
+        <v>2.732089E-2</v>
+      </c>
+      <c r="V5">
+        <v>2.42822E-3</v>
+      </c>
+      <c r="W5">
+        <v>1.8211600000000001E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23">
       <c r="A6" t="s">
         <v>71</v>
       </c>
@@ -16613,8 +16748,17 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:19">
+      <c r="U6" s="25">
+        <v>4.3914399999999999E-3</v>
+      </c>
+      <c r="V6">
+        <v>3.5601309999999997E-2</v>
+      </c>
+      <c r="W6">
+        <v>9.1340599999999994E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23">
       <c r="A7" t="s">
         <v>72</v>
       </c>
@@ -16675,8 +16819,17 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:19">
+      <c r="U7" s="25">
+        <v>1.8211600000000001E-3</v>
+      </c>
+      <c r="V7">
+        <v>3.0352700000000001E-3</v>
+      </c>
+      <c r="W7">
+        <v>3.4339809999999998E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23">
       <c r="F8" s="17">
         <v>7</v>
       </c>
@@ -16725,8 +16878,20 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:19">
+      <c r="U8">
+        <f>U5/U2</f>
+        <v>2.9921071507443362E-2</v>
+      </c>
+      <c r="V8">
+        <f t="shared" ref="V8:W8" si="5">V5/V2</f>
+        <v>0.11968419641413683</v>
+      </c>
+      <c r="W8">
+        <f t="shared" si="5"/>
+        <v>0.14822459465640717</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23">
       <c r="B9">
         <v>0.18540000000000001</v>
       </c>
@@ -16784,8 +16949,20 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:19">
+      <c r="U9">
+        <f t="shared" ref="U9:W9" si="6">U6/U3</f>
+        <v>8.060604681180053E-2</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="6"/>
+        <v>4.2853395214568921E-2</v>
+      </c>
+      <c r="W9">
+        <f t="shared" si="6"/>
+        <v>6.5982468456267429E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23">
       <c r="B10">
         <v>-3.7000000000000002E-3</v>
       </c>
@@ -16843,8 +17020,20 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:19">
+      <c r="U10">
+        <f t="shared" ref="U10:W10" si="7">U7/U4</f>
+        <v>0.74999794087850358</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="7"/>
+        <v>0.14304484516478386</v>
+      </c>
+      <c r="W10">
+        <f t="shared" si="7"/>
+        <v>6.591190401100723E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23">
       <c r="B11">
         <v>-5.1999999999999998E-3</v>
       </c>
@@ -16903,36 +17092,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:23">
       <c r="A12" t="s">
         <v>86</v>
       </c>
       <c r="N12">
-        <f t="shared" ref="N12:S12" si="5">AVERAGE(N2:N11)</f>
+        <f t="shared" ref="N12:S12" si="8">AVERAGE(N2:N11)</f>
         <v>3.5</v>
       </c>
       <c r="O12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>2.2999999999999998</v>
       </c>
       <c r="P12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.8</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>27.3</v>
       </c>
       <c r="R12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>6.9</v>
       </c>
       <c r="S12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1.2</v>
       </c>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:23">
       <c r="B13" t="s">
         <v>67</v>
       </c>
@@ -16959,7 +17148,7 @@
         <v>1.0954451150103321</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:23">
       <c r="A14" t="s">
         <v>67</v>
       </c>
@@ -16984,7 +17173,7 @@
         <v>3.435112807463534</v>
       </c>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:23">
       <c r="A15" t="s">
         <v>68</v>
       </c>
@@ -17001,7 +17190,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:23">
       <c r="A16" t="s">
         <v>69</v>
       </c>
@@ -17113,11 +17302,11 @@
         <v>0</v>
       </c>
       <c r="O18">
-        <f t="shared" ref="O18:O27" si="6">ABS(H18-L18)</f>
+        <f t="shared" ref="O18:O27" si="9">ABS(H18-L18)</f>
         <v>0</v>
       </c>
       <c r="P18">
-        <f t="shared" ref="P18:P27" si="7">ABS(I18-M18)</f>
+        <f t="shared" ref="P18:P27" si="10">ABS(I18-M18)</f>
         <v>1</v>
       </c>
       <c r="Q18">
@@ -17125,11 +17314,11 @@
         <v>0</v>
       </c>
       <c r="R18">
-        <f t="shared" ref="R18:R27" si="8">O18^2</f>
+        <f t="shared" ref="R18:R27" si="11">O18^2</f>
         <v>0</v>
       </c>
       <c r="S18">
-        <f t="shared" ref="S18:S27" si="9">P18^2</f>
+        <f t="shared" ref="S18:S27" si="12">P18^2</f>
         <v>1</v>
       </c>
     </row>
@@ -17171,27 +17360,27 @@
         <v>17</v>
       </c>
       <c r="N19">
-        <f t="shared" ref="N19:N27" si="10">ABS(G19-K19)</f>
+        <f t="shared" ref="N19:N27" si="13">ABS(G19-K19)</f>
         <v>1</v>
       </c>
       <c r="O19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="P19">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="Q19">
-        <f t="shared" ref="Q19:Q27" si="11">N19^2</f>
+        <f t="shared" ref="Q19:Q27" si="14">N19^2</f>
         <v>1</v>
       </c>
       <c r="R19">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="S19">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -17221,27 +17410,27 @@
         <v>29</v>
       </c>
       <c r="N20">
+        <f t="shared" si="13"/>
+        <v>5</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="P20">
         <f t="shared" si="10"/>
-        <v>5</v>
-      </c>
-      <c r="O20">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="P20">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q20">
+        <f t="shared" si="14"/>
+        <v>25</v>
+      </c>
+      <c r="R20">
         <f t="shared" si="11"/>
-        <v>25</v>
-      </c>
-      <c r="R20">
-        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="S20">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -17271,27 +17460,27 @@
         <v>18</v>
       </c>
       <c r="N21">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
+      <c r="O21">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="P21">
         <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="14"/>
+        <v>16</v>
+      </c>
+      <c r="R21">
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="O21">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="P21">
-        <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="Q21">
-        <f t="shared" si="11"/>
-        <v>16</v>
-      </c>
-      <c r="R21">
-        <f t="shared" si="8"/>
-        <v>4</v>
-      </c>
       <c r="S21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -17321,27 +17510,27 @@
         <v>13</v>
       </c>
       <c r="N22">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="O22">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="P22">
         <f t="shared" si="10"/>
-        <v>2</v>
-      </c>
-      <c r="O22">
-        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="R22">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="P22">
-        <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="Q22">
-        <f t="shared" si="11"/>
-        <v>4</v>
-      </c>
-      <c r="R22">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
       <c r="S22">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -17371,27 +17560,27 @@
         <v>11</v>
       </c>
       <c r="N23">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="O23">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="P23">
         <f t="shared" si="10"/>
-        <v>2</v>
-      </c>
-      <c r="O23">
-        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="P23">
-        <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="Q23">
+      <c r="R23">
         <f t="shared" si="11"/>
-        <v>4</v>
-      </c>
-      <c r="R23">
-        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="S23">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -17421,27 +17610,27 @@
         <v>69</v>
       </c>
       <c r="N24">
+        <f t="shared" si="13"/>
+        <v>12</v>
+      </c>
+      <c r="O24">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="P24">
         <f t="shared" si="10"/>
-        <v>12</v>
-      </c>
-      <c r="O24">
-        <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="P24">
-        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="Q24">
+        <f t="shared" si="14"/>
+        <v>144</v>
+      </c>
+      <c r="R24">
         <f t="shared" si="11"/>
-        <v>144</v>
-      </c>
-      <c r="R24">
-        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="S24">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
     </row>
@@ -17471,27 +17660,27 @@
         <v>15</v>
       </c>
       <c r="N25">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="O25">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="P25">
         <f t="shared" si="10"/>
-        <v>2</v>
-      </c>
-      <c r="O25">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="P25">
-        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="Q25">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="R25">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="R25">
-        <f t="shared" si="8"/>
-        <v>4</v>
-      </c>
       <c r="S25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>9</v>
       </c>
     </row>
@@ -17521,27 +17710,27 @@
         <v>6</v>
       </c>
       <c r="N26">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="P26">
         <f t="shared" si="10"/>
-        <v>2</v>
-      </c>
-      <c r="O26">
-        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="Q26">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="R26">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="P26">
-        <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="Q26">
-        <f t="shared" si="11"/>
-        <v>4</v>
-      </c>
-      <c r="R26">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
       <c r="S26">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -17571,53 +17760,53 @@
         <v>44</v>
       </c>
       <c r="N27">
+        <f t="shared" si="13"/>
+        <v>6</v>
+      </c>
+      <c r="O27">
+        <f t="shared" si="9"/>
+        <v>5</v>
+      </c>
+      <c r="P27">
         <f t="shared" si="10"/>
-        <v>6</v>
-      </c>
-      <c r="O27">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="P27">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q27">
+        <f t="shared" si="14"/>
+        <v>36</v>
+      </c>
+      <c r="R27">
         <f t="shared" si="11"/>
-        <v>36</v>
-      </c>
-      <c r="R27">
-        <f t="shared" si="8"/>
         <v>25</v>
       </c>
       <c r="S27">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:19">
       <c r="N28">
-        <f t="shared" ref="N28:S28" si="12">AVERAGE(N18:N27)</f>
+        <f t="shared" ref="N28:S28" si="15">AVERAGE(N18:N27)</f>
         <v>3.6</v>
       </c>
       <c r="O28">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="P28">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="Q28">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>23.8</v>
       </c>
       <c r="R28">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>7.8</v>
       </c>
       <c r="S28">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>1.8</v>
       </c>
     </row>
@@ -21910,14 +22099,14 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4"/>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20" t="s">
+      <c r="C1" s="24"/>
+      <c r="D1" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="20"/>
+      <c r="E1" s="24"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4"/>

--- a/results/tables/DisplayBrightness/DisplayBrightness.xlsx
+++ b/results/tables/DisplayBrightness/DisplayBrightness.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HamaKazu\Desktop\GradSchool\lab\results\tables\DisplayBrightness\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{875BAD69-A19F-4217-B727-715126A79504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD388D4-C9CD-4248-B637-981E91BD1800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FG_RGB_Trance" sheetId="8" r:id="rId1"/>
-    <sheet name="FG補正OFF" sheetId="6" r:id="rId2"/>
-    <sheet name="FGDisplay" sheetId="2" r:id="rId3"/>
-    <sheet name="画素値固定" sheetId="9" r:id="rId4"/>
-    <sheet name="BG_RGB_Trance" sheetId="7" r:id="rId5"/>
-    <sheet name="BGDisplay" sheetId="1" r:id="rId6"/>
-    <sheet name="FGLUMI" sheetId="5" r:id="rId7"/>
-    <sheet name="BGLUMI" sheetId="3" r:id="rId8"/>
-    <sheet name="BG補正OFF" sheetId="4" r:id="rId9"/>
+    <sheet name="ColorLumi" sheetId="10" r:id="rId2"/>
+    <sheet name="FG補正OFF" sheetId="6" r:id="rId3"/>
+    <sheet name="FGDisplay" sheetId="2" r:id="rId4"/>
+    <sheet name="画素値固定" sheetId="9" r:id="rId5"/>
+    <sheet name="BG_RGB_Trance" sheetId="7" r:id="rId6"/>
+    <sheet name="BGDisplay" sheetId="1" r:id="rId7"/>
+    <sheet name="FGLUMI" sheetId="5" r:id="rId8"/>
+    <sheet name="BGLUMI" sheetId="3" r:id="rId9"/>
+    <sheet name="BG補正OFF" sheetId="4" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="144">
   <si>
     <t>標準光</t>
     <rPh sb="0" eb="2">
@@ -621,6 +622,46 @@
     <t>Pixel: 90</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>std</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Y_L</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>x</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>y</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BG</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BG_T</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FG</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FG_R</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Black</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Y_L-BL</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -789,11 +830,11 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -12706,7 +12747,7 @@
         <f>P2^2</f>
         <v>1</v>
       </c>
-      <c r="U2" s="25">
+      <c r="U2" s="24">
         <v>0.91309865000000001</v>
       </c>
       <c r="V2">
@@ -12777,7 +12818,7 @@
         <f t="shared" ref="S3:S11" si="5">P3^2</f>
         <v>4</v>
       </c>
-      <c r="U3" s="25">
+      <c r="U3" s="24">
         <v>5.7805429999999998E-2</v>
       </c>
       <c r="V3">
@@ -12848,7 +12889,7 @@
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="U4" s="25">
+      <c r="U4" s="24">
         <v>2.1246899999999998E-3</v>
       </c>
       <c r="V4">
@@ -12919,7 +12960,7 @@
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="U5" s="25">
+      <c r="U5" s="24">
         <v>0.25015828000000001</v>
       </c>
       <c r="V5">
@@ -12990,7 +13031,7 @@
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
-      <c r="U6" s="25">
+      <c r="U6" s="24">
         <v>1.680738E-2</v>
       </c>
       <c r="V6">
@@ -13061,7 +13102,7 @@
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="U7" s="25">
+      <c r="U7" s="24">
         <v>2.1246899999999998E-3</v>
       </c>
       <c r="V7">
@@ -14103,21 +14144,21 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{705515B1-704B-422E-A4FC-01586B06F9C2}">
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F91A220-ECA8-426C-9CB4-6411C694E3C1}">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4"/>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24" t="s">
+      <c r="C1" s="25"/>
+      <c r="D1" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="24"/>
+      <c r="E1" s="25"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4"/>
@@ -14139,16 +14180,16 @@
         <v>57</v>
       </c>
       <c r="B3" s="6">
-        <v>0.71633999999999998</v>
+        <v>0.69745999999999997</v>
       </c>
       <c r="C3" s="6">
-        <v>8.1040000000000001E-2</v>
+        <v>0.10964</v>
       </c>
       <c r="D3" s="6">
-        <v>0.63109999999999999</v>
+        <v>0.60734999999999995</v>
       </c>
       <c r="E3" s="6">
-        <v>0.10315000000000001</v>
+        <v>0.10181</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -14156,16 +14197,16 @@
         <v>56</v>
       </c>
       <c r="B4" s="8">
-        <v>0.67437000000000002</v>
+        <v>0.71084000000000003</v>
       </c>
       <c r="C4" s="8">
-        <v>0.11149000000000001</v>
+        <v>0.13605</v>
       </c>
       <c r="D4" s="8">
-        <v>0.69220999999999999</v>
+        <v>0.67515999999999998</v>
       </c>
       <c r="E4" s="8">
-        <v>0.12063</v>
+        <v>0.13703000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -14178,7 +14219,1345 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C5C25D5-A457-4A5B-BC5A-4FA1B685C426}">
+  <dimension ref="A1:P35"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="A1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="B2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J2" t="s">
+        <v>69</v>
+      </c>
+      <c r="N2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="B3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G3" t="s">
+        <v>143</v>
+      </c>
+      <c r="H3" t="s">
+        <v>136</v>
+      </c>
+      <c r="I3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J3" t="s">
+        <v>135</v>
+      </c>
+      <c r="K3" t="s">
+        <v>143</v>
+      </c>
+      <c r="L3" t="s">
+        <v>136</v>
+      </c>
+      <c r="M3" t="s">
+        <v>137</v>
+      </c>
+      <c r="N3" t="s">
+        <v>135</v>
+      </c>
+      <c r="O3" t="s">
+        <v>136</v>
+      </c>
+      <c r="P3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>40.4</v>
+      </c>
+      <c r="C4">
+        <f>B4-$N$4</f>
+        <v>40</v>
+      </c>
+      <c r="D4">
+        <v>0.64319999999999999</v>
+      </c>
+      <c r="E4">
+        <v>0.32840000000000003</v>
+      </c>
+      <c r="F4">
+        <v>150.9</v>
+      </c>
+      <c r="G4">
+        <f>F4-$N$4</f>
+        <v>150.5</v>
+      </c>
+      <c r="H4">
+        <v>0.30769999999999997</v>
+      </c>
+      <c r="I4">
+        <v>0.59599999999999997</v>
+      </c>
+      <c r="J4">
+        <v>13.2</v>
+      </c>
+      <c r="K4">
+        <f>J4-$N$4</f>
+        <v>12.799999999999999</v>
+      </c>
+      <c r="L4">
+        <v>0.1547</v>
+      </c>
+      <c r="M4">
+        <v>5.1700000000000003E-2</v>
+      </c>
+      <c r="N4">
+        <v>0.4</v>
+      </c>
+      <c r="O4">
+        <v>0.17910000000000001</v>
+      </c>
+      <c r="P4">
+        <v>0.28210000000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>40</v>
+      </c>
+      <c r="C5">
+        <f t="shared" ref="C5:C6" si="0">B5-$N$4</f>
+        <v>39.6</v>
+      </c>
+      <c r="D5">
+        <v>0.64229999999999998</v>
+      </c>
+      <c r="E5">
+        <v>0.32779999999999998</v>
+      </c>
+      <c r="F5">
+        <v>151</v>
+      </c>
+      <c r="G5">
+        <f t="shared" ref="G5:G6" si="1">F5-$N$4</f>
+        <v>150.6</v>
+      </c>
+      <c r="H5">
+        <v>0.30730000000000002</v>
+      </c>
+      <c r="I5">
+        <v>0.59589999999999999</v>
+      </c>
+      <c r="J5">
+        <v>13.1</v>
+      </c>
+      <c r="K5">
+        <f t="shared" ref="K5:K6" si="2">J5-$N$4</f>
+        <v>12.7</v>
+      </c>
+      <c r="L5">
+        <v>0.15459999999999999</v>
+      </c>
+      <c r="M5">
+        <v>5.16E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>40</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>39.6</v>
+      </c>
+      <c r="D6">
+        <v>0.64259999999999995</v>
+      </c>
+      <c r="E6">
+        <v>0.32829999999999998</v>
+      </c>
+      <c r="F6">
+        <v>151</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="1"/>
+        <v>150.6</v>
+      </c>
+      <c r="H6">
+        <v>0.30719999999999997</v>
+      </c>
+      <c r="I6">
+        <v>0.59570000000000001</v>
+      </c>
+      <c r="J6">
+        <v>13.1</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="2"/>
+        <v>12.7</v>
+      </c>
+      <c r="L6">
+        <v>0.1545</v>
+      </c>
+      <c r="M6">
+        <v>5.16E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7">
+        <f>AVERAGE(B4:B6)</f>
+        <v>40.133333333333333</v>
+      </c>
+      <c r="C7">
+        <f t="shared" ref="C7:K7" si="3">AVERAGE(C4:C6)</f>
+        <v>39.733333333333327</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="3"/>
+        <v>0.64269999999999994</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="3"/>
+        <v>0.32816666666666666</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="3"/>
+        <v>150.96666666666667</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="3"/>
+        <v>150.56666666666669</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="3"/>
+        <v>0.30739999999999995</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="3"/>
+        <v>0.59586666666666666</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="3"/>
+        <v>13.133333333333333</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="3"/>
+        <v>12.733333333333334</v>
+      </c>
+      <c r="L7">
+        <f>AVERAGE(L4:L6)</f>
+        <v>0.15459999999999999</v>
+      </c>
+      <c r="M7">
+        <f>AVERAGE(M4:M6)</f>
+        <v>5.1633333333333337E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" t="s">
+        <v>134</v>
+      </c>
+      <c r="B8">
+        <f>_xlfn.STDEV.P(B4:B6)</f>
+        <v>0.18856180831641201</v>
+      </c>
+      <c r="C8">
+        <f t="shared" ref="C8:K8" si="4">_xlfn.STDEV.P(C4:C6)</f>
+        <v>0.18856180831641201</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="4"/>
+        <v>3.7416573867740237E-4</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="4"/>
+        <v>2.6246692913374042E-4</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="4"/>
+        <v>4.7140452079100489E-2</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="4"/>
+        <v>4.7140452079100489E-2</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="4"/>
+        <v>2.1602468994692199E-4</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="4"/>
+        <v>1.2472191289245098E-4</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="4"/>
+        <v>4.7140452079103001E-2</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="4"/>
+        <v>4.7140452079103001E-2</v>
+      </c>
+      <c r="L8">
+        <f>_xlfn.STDEV.P(L4:L6)</f>
+        <v>8.164965809277494E-5</v>
+      </c>
+      <c r="M8">
+        <f>_xlfn.STDEV.P(M4:M6)</f>
+        <v>4.7140452079104518E-5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="B11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" t="s">
+        <v>68</v>
+      </c>
+      <c r="J11" t="s">
+        <v>69</v>
+      </c>
+      <c r="N11" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="B12" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" t="s">
+        <v>143</v>
+      </c>
+      <c r="D12" t="s">
+        <v>136</v>
+      </c>
+      <c r="E12" t="s">
+        <v>137</v>
+      </c>
+      <c r="F12" t="s">
+        <v>135</v>
+      </c>
+      <c r="G12" t="s">
+        <v>143</v>
+      </c>
+      <c r="H12" t="s">
+        <v>136</v>
+      </c>
+      <c r="I12" t="s">
+        <v>137</v>
+      </c>
+      <c r="J12" t="s">
+        <v>135</v>
+      </c>
+      <c r="K12" t="s">
+        <v>143</v>
+      </c>
+      <c r="L12" t="s">
+        <v>136</v>
+      </c>
+      <c r="M12" t="s">
+        <v>137</v>
+      </c>
+      <c r="N12" t="s">
+        <v>135</v>
+      </c>
+      <c r="O12" t="s">
+        <v>136</v>
+      </c>
+      <c r="P12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>7.2</v>
+      </c>
+      <c r="C13">
+        <f>B13-$N$13</f>
+        <v>7.1000000000000005</v>
+      </c>
+      <c r="D13">
+        <v>0.62770000000000004</v>
+      </c>
+      <c r="E13">
+        <v>0.32179999999999997</v>
+      </c>
+      <c r="F13">
+        <v>31.7</v>
+      </c>
+      <c r="G13">
+        <f>F13-$N$13</f>
+        <v>31.599999999999998</v>
+      </c>
+      <c r="H13">
+        <v>0.29370000000000002</v>
+      </c>
+      <c r="I13">
+        <v>0.58940000000000003</v>
+      </c>
+      <c r="J13">
+        <v>3.2</v>
+      </c>
+      <c r="K13">
+        <f>J13-$N$13</f>
+        <v>3.1</v>
+      </c>
+      <c r="L13">
+        <v>0.15479999999999999</v>
+      </c>
+      <c r="M13">
+        <v>4.7E-2</v>
+      </c>
+      <c r="N13">
+        <v>0.1</v>
+      </c>
+      <c r="O13">
+        <v>0.42099999999999999</v>
+      </c>
+      <c r="P13">
+        <v>0.217</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
+        <v>7.3</v>
+      </c>
+      <c r="C14">
+        <f t="shared" ref="C14:C15" si="5">B14-$N$13</f>
+        <v>7.2</v>
+      </c>
+      <c r="D14">
+        <v>0.62839999999999996</v>
+      </c>
+      <c r="E14">
+        <v>0.32440000000000002</v>
+      </c>
+      <c r="F14">
+        <v>31.7</v>
+      </c>
+      <c r="G14">
+        <f t="shared" ref="G14:G15" si="6">F14-$N$13</f>
+        <v>31.599999999999998</v>
+      </c>
+      <c r="H14">
+        <v>0.2954</v>
+      </c>
+      <c r="I14">
+        <v>0.58909999999999996</v>
+      </c>
+      <c r="J14">
+        <v>3.2</v>
+      </c>
+      <c r="K14">
+        <f t="shared" ref="K14:K15" si="7">J14-$N$13</f>
+        <v>3.1</v>
+      </c>
+      <c r="L14">
+        <v>0.15479999999999999</v>
+      </c>
+      <c r="M14">
+        <v>4.65E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15">
+        <v>3</v>
+      </c>
+      <c r="B15">
+        <v>7.3</v>
+      </c>
+      <c r="C15">
+        <f>B15-$N$13</f>
+        <v>7.2</v>
+      </c>
+      <c r="D15">
+        <v>0.63049999999999995</v>
+      </c>
+      <c r="E15">
+        <v>0.32940000000000003</v>
+      </c>
+      <c r="F15">
+        <v>31.7</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="6"/>
+        <v>31.599999999999998</v>
+      </c>
+      <c r="H15">
+        <v>0.29370000000000002</v>
+      </c>
+      <c r="I15">
+        <v>0.58919999999999995</v>
+      </c>
+      <c r="J15">
+        <v>3.2</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="7"/>
+        <v>3.1</v>
+      </c>
+      <c r="L15">
+        <v>0.15459999999999999</v>
+      </c>
+      <c r="M15">
+        <v>4.6600000000000003E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16">
+        <f>AVERAGE(B13:B15)</f>
+        <v>7.2666666666666666</v>
+      </c>
+      <c r="C16">
+        <f t="shared" ref="C16:K16" si="8">AVERAGE(C13:C15)</f>
+        <v>7.166666666666667</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="8"/>
+        <v>0.62886666666666668</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="8"/>
+        <v>0.32519999999999999</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="8"/>
+        <v>31.7</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="8"/>
+        <v>31.599999999999998</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="8"/>
+        <v>0.29426666666666668</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="8"/>
+        <v>0.58923333333333339</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="8"/>
+        <v>3.2000000000000006</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="8"/>
+        <v>3.1</v>
+      </c>
+      <c r="L16">
+        <f>AVERAGE(L13:L15)</f>
+        <v>0.15473333333333331</v>
+      </c>
+      <c r="M16">
+        <f>AVERAGE(M13:M15)</f>
+        <v>4.6699999999999998E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" t="s">
+        <v>134</v>
+      </c>
+      <c r="B17">
+        <f>_xlfn.STDEV.P(B13:B15)</f>
+        <v>4.7140452079103001E-2</v>
+      </c>
+      <c r="C17">
+        <f t="shared" ref="C17:K17" si="9">_xlfn.STDEV.P(C13:C15)</f>
+        <v>4.7140452079103001E-2</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="9"/>
+        <v>1.189771219838287E-3</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="9"/>
+        <v>3.1538336460039847E-3</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="9"/>
+        <v>8.0138768534474415E-4</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="9"/>
+        <v>1.2472191289250044E-4</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="9"/>
+        <v>4.4408920985006262E-16</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <f>_xlfn.STDEV.P(L13:L15)</f>
+        <v>9.4280904158209036E-5</v>
+      </c>
+      <c r="M17">
+        <f>_xlfn.STDEV.P(M13:M15)</f>
+        <v>2.1602468994692844E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="B20" t="s">
+        <v>67</v>
+      </c>
+      <c r="F20" t="s">
+        <v>68</v>
+      </c>
+      <c r="J20" t="s">
+        <v>69</v>
+      </c>
+      <c r="N20" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="B21" t="s">
+        <v>135</v>
+      </c>
+      <c r="C21" t="s">
+        <v>143</v>
+      </c>
+      <c r="D21" t="s">
+        <v>136</v>
+      </c>
+      <c r="E21" t="s">
+        <v>137</v>
+      </c>
+      <c r="F21" t="s">
+        <v>135</v>
+      </c>
+      <c r="G21" t="s">
+        <v>143</v>
+      </c>
+      <c r="H21" t="s">
+        <v>136</v>
+      </c>
+      <c r="I21" t="s">
+        <v>137</v>
+      </c>
+      <c r="J21" t="s">
+        <v>135</v>
+      </c>
+      <c r="K21" t="s">
+        <v>143</v>
+      </c>
+      <c r="L21" t="s">
+        <v>136</v>
+      </c>
+      <c r="M21" t="s">
+        <v>137</v>
+      </c>
+      <c r="N21" t="s">
+        <v>135</v>
+      </c>
+      <c r="O21" t="s">
+        <v>136</v>
+      </c>
+      <c r="P21" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22">
+        <v>1</v>
+      </c>
+      <c r="B22">
+        <v>30.7</v>
+      </c>
+      <c r="C22">
+        <f>B22-$N$22</f>
+        <v>30.4</v>
+      </c>
+      <c r="D22">
+        <v>0.65690000000000004</v>
+      </c>
+      <c r="E22">
+        <v>0.3201</v>
+      </c>
+      <c r="F22">
+        <v>114.5</v>
+      </c>
+      <c r="G22">
+        <f>F22-$N$22</f>
+        <v>114.2</v>
+      </c>
+      <c r="H22">
+        <v>0.3276</v>
+      </c>
+      <c r="I22">
+        <v>0.61439999999999995</v>
+      </c>
+      <c r="J22">
+        <v>11.5</v>
+      </c>
+      <c r="K22">
+        <f>J22-$N$22</f>
+        <v>11.2</v>
+      </c>
+      <c r="L22">
+        <v>0.15659999999999999</v>
+      </c>
+      <c r="M22">
+        <v>4.8899999999999999E-2</v>
+      </c>
+      <c r="N22">
+        <v>0.3</v>
+      </c>
+      <c r="O22">
+        <v>0.2702</v>
+      </c>
+      <c r="P22">
+        <v>0.26229999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23">
+        <v>2</v>
+      </c>
+      <c r="B23">
+        <v>30.8</v>
+      </c>
+      <c r="C23">
+        <f t="shared" ref="C23:C24" si="10">B23-$N$22</f>
+        <v>30.5</v>
+      </c>
+      <c r="D23">
+        <v>0.65800000000000003</v>
+      </c>
+      <c r="E23">
+        <v>0.32040000000000002</v>
+      </c>
+      <c r="F23">
+        <v>114</v>
+      </c>
+      <c r="G23">
+        <f t="shared" ref="G23:G24" si="11">F23-$N$22</f>
+        <v>113.7</v>
+      </c>
+      <c r="H23">
+        <v>0.32969999999999999</v>
+      </c>
+      <c r="I23">
+        <v>0.61380000000000001</v>
+      </c>
+      <c r="J23">
+        <v>11.5</v>
+      </c>
+      <c r="K23">
+        <f t="shared" ref="K23:K24" si="12">J23-$N$22</f>
+        <v>11.2</v>
+      </c>
+      <c r="L23">
+        <v>0.1598</v>
+      </c>
+      <c r="M23">
+        <v>4.99E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24">
+        <v>30.9</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="10"/>
+        <v>30.599999999999998</v>
+      </c>
+      <c r="D24">
+        <v>0.65610000000000002</v>
+      </c>
+      <c r="E24">
+        <v>0.32129999999999997</v>
+      </c>
+      <c r="F24">
+        <v>114.4</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="11"/>
+        <v>114.10000000000001</v>
+      </c>
+      <c r="H24">
+        <v>0.32969999999999999</v>
+      </c>
+      <c r="I24">
+        <v>0.61380000000000001</v>
+      </c>
+      <c r="J24">
+        <v>11.4</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="12"/>
+        <v>11.1</v>
+      </c>
+      <c r="L24">
+        <v>0.16220000000000001</v>
+      </c>
+      <c r="M24">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25">
+        <f>AVERAGE(B22:B24)</f>
+        <v>30.8</v>
+      </c>
+      <c r="C25">
+        <f t="shared" ref="C25:K25" si="13">AVERAGE(C22:C24)</f>
+        <v>30.5</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="13"/>
+        <v>0.65700000000000003</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="13"/>
+        <v>0.3206</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="13"/>
+        <v>114.3</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="13"/>
+        <v>114</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="13"/>
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="13"/>
+        <v>0.61399999999999999</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="13"/>
+        <v>11.466666666666667</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="13"/>
+        <v>11.166666666666666</v>
+      </c>
+      <c r="L25">
+        <f>AVERAGE(L22:L24)</f>
+        <v>0.15953333333333333</v>
+      </c>
+      <c r="M25">
+        <f>AVERAGE(M22:M24)</f>
+        <v>4.9599999999999998E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26" t="s">
+        <v>134</v>
+      </c>
+      <c r="B26">
+        <f>_xlfn.STDEV.P(B22:B24)</f>
+        <v>8.1649658092772318E-2</v>
+      </c>
+      <c r="C26">
+        <f t="shared" ref="C26:K26" si="14">_xlfn.STDEV.P(C22:C24)</f>
+        <v>8.1649658092772318E-2</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="14"/>
+        <v>7.7888809636986601E-4</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="14"/>
+        <v>5.0990195135926588E-4</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="14"/>
+        <v>0.21602468994692955</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="14"/>
+        <v>0.21602468994692955</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="14"/>
+        <v>9.8994949366116225E-4</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="14"/>
+        <v>2.828427124745879E-4</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="14"/>
+        <v>4.7140452079103001E-2</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="14"/>
+        <v>4.7140452079103001E-2</v>
+      </c>
+      <c r="L26">
+        <f>_xlfn.STDEV.P(L22:L24)</f>
+        <v>2.2939534045447094E-3</v>
+      </c>
+      <c r="M26">
+        <f>_xlfn.STDEV.P(M22:M24)</f>
+        <v>4.9665548085837919E-4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="B29" t="s">
+        <v>67</v>
+      </c>
+      <c r="F29" t="s">
+        <v>68</v>
+      </c>
+      <c r="J29" t="s">
+        <v>69</v>
+      </c>
+      <c r="N29" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="B30" t="s">
+        <v>135</v>
+      </c>
+      <c r="C30" t="s">
+        <v>143</v>
+      </c>
+      <c r="D30" t="s">
+        <v>136</v>
+      </c>
+      <c r="E30" t="s">
+        <v>137</v>
+      </c>
+      <c r="F30" t="s">
+        <v>135</v>
+      </c>
+      <c r="G30" t="s">
+        <v>143</v>
+      </c>
+      <c r="H30" t="s">
+        <v>136</v>
+      </c>
+      <c r="I30" t="s">
+        <v>137</v>
+      </c>
+      <c r="J30" t="s">
+        <v>135</v>
+      </c>
+      <c r="K30" t="s">
+        <v>143</v>
+      </c>
+      <c r="L30" t="s">
+        <v>136</v>
+      </c>
+      <c r="M30" t="s">
+        <v>137</v>
+      </c>
+      <c r="N30" t="s">
+        <v>135</v>
+      </c>
+      <c r="O30" t="s">
+        <v>136</v>
+      </c>
+      <c r="P30" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31">
+        <v>1</v>
+      </c>
+      <c r="B31">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="C31">
+        <f>B31-$N$31</f>
+        <v>20.2</v>
+      </c>
+      <c r="D31">
+        <v>0.64349999999999996</v>
+      </c>
+      <c r="E31">
+        <v>0.33229999999999998</v>
+      </c>
+      <c r="F31">
+        <v>73.7</v>
+      </c>
+      <c r="G31">
+        <f>F31-$N$31</f>
+        <v>73.5</v>
+      </c>
+      <c r="H31">
+        <v>0.31950000000000001</v>
+      </c>
+      <c r="I31">
+        <v>0.62309999999999999</v>
+      </c>
+      <c r="J31">
+        <v>7</v>
+      </c>
+      <c r="K31">
+        <f>J31-$N$31</f>
+        <v>6.8</v>
+      </c>
+      <c r="L31">
+        <v>0.15279999999999999</v>
+      </c>
+      <c r="M31">
+        <v>5.1499999999999997E-2</v>
+      </c>
+      <c r="N31">
+        <v>0.2</v>
+      </c>
+      <c r="O31">
+        <v>0.21340000000000001</v>
+      </c>
+      <c r="P31">
+        <v>0.18429999999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32">
+        <v>2</v>
+      </c>
+      <c r="B32">
+        <v>20.3</v>
+      </c>
+      <c r="C32">
+        <f t="shared" ref="C32:C33" si="15">B32-$N$31</f>
+        <v>20.100000000000001</v>
+      </c>
+      <c r="D32">
+        <v>0.64549999999999996</v>
+      </c>
+      <c r="E32">
+        <v>0.33260000000000001</v>
+      </c>
+      <c r="F32">
+        <v>73.7</v>
+      </c>
+      <c r="G32">
+        <f t="shared" ref="G32:G33" si="16">F32-$N$31</f>
+        <v>73.5</v>
+      </c>
+      <c r="H32">
+        <v>0.32</v>
+      </c>
+      <c r="I32">
+        <v>0.62460000000000004</v>
+      </c>
+      <c r="J32">
+        <v>7</v>
+      </c>
+      <c r="K32">
+        <f t="shared" ref="K32:K33" si="17">J32-$N$31</f>
+        <v>6.8</v>
+      </c>
+      <c r="L32">
+        <v>0.1527</v>
+      </c>
+      <c r="M32">
+        <v>5.1299999999999998E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33">
+        <v>3</v>
+      </c>
+      <c r="B33">
+        <v>20.3</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="15"/>
+        <v>20.100000000000001</v>
+      </c>
+      <c r="D33">
+        <v>0.64610000000000001</v>
+      </c>
+      <c r="E33">
+        <v>0.33239999999999997</v>
+      </c>
+      <c r="F33">
+        <v>73.7</v>
+      </c>
+      <c r="G33">
+        <f t="shared" si="16"/>
+        <v>73.5</v>
+      </c>
+      <c r="H33">
+        <v>0.31890000000000002</v>
+      </c>
+      <c r="I33">
+        <v>0.62370000000000003</v>
+      </c>
+      <c r="J33">
+        <v>7</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="17"/>
+        <v>6.8</v>
+      </c>
+      <c r="L33">
+        <v>0.15179999999999999</v>
+      </c>
+      <c r="M33">
+        <v>5.1700000000000003E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" t="s">
+        <v>86</v>
+      </c>
+      <c r="B34">
+        <f>AVERAGE(B31:B33)</f>
+        <v>20.333333333333332</v>
+      </c>
+      <c r="C34">
+        <f t="shared" ref="C34:K34" si="18">AVERAGE(C31:C33)</f>
+        <v>20.133333333333333</v>
+      </c>
+      <c r="D34">
+        <f t="shared" si="18"/>
+        <v>0.64503333333333324</v>
+      </c>
+      <c r="E34">
+        <f t="shared" si="18"/>
+        <v>0.33243333333333336</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="18"/>
+        <v>73.7</v>
+      </c>
+      <c r="G34">
+        <f t="shared" si="18"/>
+        <v>73.5</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="18"/>
+        <v>0.31946666666666662</v>
+      </c>
+      <c r="I34">
+        <f t="shared" si="18"/>
+        <v>0.62380000000000002</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="18"/>
+        <v>7</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="18"/>
+        <v>6.8</v>
+      </c>
+      <c r="L34">
+        <f>AVERAGE(L31:L33)</f>
+        <v>0.15243333333333334</v>
+      </c>
+      <c r="M34">
+        <f>AVERAGE(M31:M33)</f>
+        <v>5.1499999999999997E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" t="s">
+        <v>134</v>
+      </c>
+      <c r="B35">
+        <f>_xlfn.STDEV.P(B31:B33)</f>
+        <v>4.7140452079102169E-2</v>
+      </c>
+      <c r="C35">
+        <f t="shared" ref="C35:K35" si="19">_xlfn.STDEV.P(C31:C33)</f>
+        <v>4.7140452079102169E-2</v>
+      </c>
+      <c r="D35">
+        <f t="shared" si="19"/>
+        <v>1.1115554667022196E-3</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="19"/>
+        <v>1.247219128924757E-4</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="19"/>
+        <v>4.4969125210773047E-4</v>
+      </c>
+      <c r="I35">
+        <f t="shared" si="19"/>
+        <v>6.1644140029691976E-4</v>
+      </c>
+      <c r="J35">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <f>_xlfn.STDEV.P(L31:L33)</f>
+        <v>4.496912521077373E-4</v>
+      </c>
+      <c r="M35">
+        <f>_xlfn.STDEV.P(M31:M33)</f>
+        <v>1.6329931618554703E-4</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{705515B1-704B-422E-A4FC-01586B06F9C2}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="4"/>
+      <c r="B1" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="25"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="6">
+        <v>0.71633999999999998</v>
+      </c>
+      <c r="C3" s="6">
+        <v>8.1040000000000001E-2</v>
+      </c>
+      <c r="D3" s="6">
+        <v>0.63109999999999999</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0.10315000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.67437000000000002</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.11149000000000001</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.69220999999999999</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0.12063</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E3B391E-8AA8-4A22-96DE-5B9DDC22536B}">
   <dimension ref="A1:T82"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -15714,7 +17093,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E63BFBA-8482-4406-A3A3-55ADB73C3469}">
   <dimension ref="A1:L19"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -16344,7 +17723,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50473ED6-92DB-49CB-BB73-3D59C4C4199E}">
   <dimension ref="A1:W31"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -16464,7 +17843,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U2" s="25">
+      <c r="U2" s="24">
         <v>0.91309865000000001</v>
       </c>
       <c r="V2">
@@ -16535,7 +17914,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U3" s="25">
+      <c r="U3" s="24">
         <v>5.4480279999999999E-2</v>
       </c>
       <c r="V3">
@@ -16606,7 +17985,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U4" s="25">
+      <c r="U4" s="24">
         <v>2.42822E-3</v>
       </c>
       <c r="V4">
@@ -16677,7 +18056,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U5" s="25">
+      <c r="U5" s="24">
         <v>2.732089E-2</v>
       </c>
       <c r="V5">
@@ -16748,7 +18127,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U6" s="25">
+      <c r="U6" s="24">
         <v>4.3914399999999999E-3</v>
       </c>
       <c r="V6">
@@ -16819,7 +18198,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="U7" s="25">
+      <c r="U7" s="24">
         <v>1.8211600000000001E-3</v>
       </c>
       <c r="V7">
@@ -17852,7 +19231,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q89"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -19935,7 +21314,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{748D88B3-AB89-451F-B4F0-D6322845623C}">
   <dimension ref="A1:AF20"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -20961,7 +22340,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4F1D99B-35E9-4F54-9502-3DA711A1E317}">
   <dimension ref="A1:AF25"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -22090,79 +23469,4 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F91A220-ECA8-426C-9CB4-6411C694E3C1}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="18"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="4"/>
-      <c r="B1" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" s="24"/>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3" s="6">
-        <v>0.69745999999999997</v>
-      </c>
-      <c r="C3" s="6">
-        <v>0.10964</v>
-      </c>
-      <c r="D3" s="6">
-        <v>0.60734999999999995</v>
-      </c>
-      <c r="E3" s="6">
-        <v>0.10181</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.71084000000000003</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.13605</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.67515999999999998</v>
-      </c>
-      <c r="E4" s="8">
-        <v>0.13703000000000001</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-  </mergeCells>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/results/tables/DisplayBrightness/DisplayBrightness.xlsx
+++ b/results/tables/DisplayBrightness/DisplayBrightness.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HamaKazu\Desktop\GradSchool\lab\results\tables\DisplayBrightness\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD388D4-C9CD-4248-B637-981E91BD1800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7F4A0DB-744D-4C1E-A76C-57338B008278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="142">
   <si>
     <t>標準光</t>
     <rPh sb="0" eb="2">
@@ -639,15 +639,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>BG</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>BG_T</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>FG</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -14221,7 +14213,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C5C25D5-A457-4A5B-BC5A-4FA1B685C426}">
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -14240,7 +14232,7 @@
         <v>69</v>
       </c>
       <c r="N2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -14248,7 +14240,7 @@
         <v>135</v>
       </c>
       <c r="C3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D3" t="s">
         <v>136</v>
@@ -14260,7 +14252,7 @@
         <v>135</v>
       </c>
       <c r="G3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H3" t="s">
         <v>136</v>
@@ -14272,7 +14264,7 @@
         <v>135</v>
       </c>
       <c r="K3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L3" t="s">
         <v>136</v>
@@ -14295,43 +14287,31 @@
         <v>1</v>
       </c>
       <c r="B4">
-        <v>40.4</v>
-      </c>
-      <c r="C4">
-        <f>B4-$N$4</f>
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D4">
-        <v>0.64319999999999999</v>
+        <v>0.62949999999999995</v>
       </c>
       <c r="E4">
-        <v>0.32840000000000003</v>
+        <v>0.32700000000000001</v>
       </c>
       <c r="F4">
-        <v>150.9</v>
-      </c>
-      <c r="G4">
-        <f>F4-$N$4</f>
-        <v>150.5</v>
+        <v>34.4</v>
       </c>
       <c r="H4">
-        <v>0.30769999999999997</v>
+        <v>0.30359999999999998</v>
       </c>
       <c r="I4">
-        <v>0.59599999999999997</v>
+        <v>0.62809999999999999</v>
       </c>
       <c r="J4">
-        <v>13.2</v>
-      </c>
-      <c r="K4">
-        <f>J4-$N$4</f>
-        <v>12.799999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="L4">
-        <v>0.1547</v>
+        <v>0.15459999999999999</v>
       </c>
       <c r="M4">
-        <v>5.1700000000000003E-2</v>
+        <v>4.58E-2</v>
       </c>
       <c r="N4">
         <v>0.4</v>
@@ -14348,43 +14328,31 @@
         <v>2</v>
       </c>
       <c r="B5">
-        <v>40</v>
-      </c>
-      <c r="C5">
-        <f t="shared" ref="C5:C6" si="0">B5-$N$4</f>
-        <v>39.6</v>
+        <v>8</v>
       </c>
       <c r="D5">
-        <v>0.64229999999999998</v>
+        <v>0.63429999999999997</v>
       </c>
       <c r="E5">
-        <v>0.32779999999999998</v>
+        <v>0.33029999999999998</v>
       </c>
       <c r="F5">
-        <v>151</v>
-      </c>
-      <c r="G5">
-        <f t="shared" ref="G5:G6" si="1">F5-$N$4</f>
-        <v>150.6</v>
+        <v>34.299999999999997</v>
       </c>
       <c r="H5">
-        <v>0.30730000000000002</v>
+        <v>0.30349999999999999</v>
       </c>
       <c r="I5">
-        <v>0.59589999999999999</v>
+        <v>0.62590000000000001</v>
       </c>
       <c r="J5">
-        <v>13.1</v>
-      </c>
-      <c r="K5">
-        <f t="shared" ref="K5:K6" si="2">J5-$N$4</f>
-        <v>12.7</v>
+        <v>3.6</v>
       </c>
       <c r="L5">
         <v>0.15459999999999999</v>
       </c>
       <c r="M5">
-        <v>5.16E-2</v>
+        <v>4.5699999999999998E-2</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -14392,43 +14360,31 @@
         <v>3</v>
       </c>
       <c r="B6">
-        <v>40</v>
-      </c>
-      <c r="C6">
-        <f t="shared" si="0"/>
-        <v>39.6</v>
+        <v>8</v>
       </c>
       <c r="D6">
-        <v>0.64259999999999995</v>
+        <v>0.627</v>
       </c>
       <c r="E6">
-        <v>0.32829999999999998</v>
+        <v>0.32850000000000001</v>
       </c>
       <c r="F6">
-        <v>151</v>
-      </c>
-      <c r="G6">
-        <f t="shared" si="1"/>
-        <v>150.6</v>
+        <v>34.4</v>
       </c>
       <c r="H6">
-        <v>0.30719999999999997</v>
+        <v>0.30480000000000002</v>
       </c>
       <c r="I6">
-        <v>0.59570000000000001</v>
+        <v>0.62519999999999998</v>
       </c>
       <c r="J6">
-        <v>13.1</v>
-      </c>
-      <c r="K6">
-        <f t="shared" si="2"/>
-        <v>12.7</v>
+        <v>3.6</v>
       </c>
       <c r="L6">
-        <v>0.1545</v>
+        <v>0.15379999999999999</v>
       </c>
       <c r="M6">
-        <v>5.16E-2</v>
+        <v>4.5699999999999998E-2</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -14437,51 +14393,51 @@
       </c>
       <c r="B7">
         <f>AVERAGE(B4:B6)</f>
-        <v>40.133333333333333</v>
-      </c>
-      <c r="C7">
-        <f t="shared" ref="C7:K7" si="3">AVERAGE(C4:C6)</f>
-        <v>39.733333333333327</v>
+        <v>8</v>
+      </c>
+      <c r="C7" t="e">
+        <f t="shared" ref="C7:M7" si="0">AVERAGE(C4:C6)</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="D7">
-        <f t="shared" si="3"/>
-        <v>0.64269999999999994</v>
+        <f t="shared" si="0"/>
+        <v>0.63026666666666664</v>
       </c>
       <c r="E7">
-        <f t="shared" si="3"/>
-        <v>0.32816666666666666</v>
+        <f t="shared" si="0"/>
+        <v>0.3286</v>
       </c>
       <c r="F7">
-        <f t="shared" si="3"/>
-        <v>150.96666666666667</v>
-      </c>
-      <c r="G7">
-        <f t="shared" si="3"/>
-        <v>150.56666666666669</v>
+        <f t="shared" si="0"/>
+        <v>34.366666666666667</v>
+      </c>
+      <c r="G7" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="H7">
-        <f t="shared" si="3"/>
-        <v>0.30739999999999995</v>
+        <f t="shared" si="0"/>
+        <v>0.30396666666666666</v>
       </c>
       <c r="I7">
-        <f t="shared" si="3"/>
-        <v>0.59586666666666666</v>
+        <f t="shared" si="0"/>
+        <v>0.62639999999999996</v>
       </c>
       <c r="J7">
-        <f t="shared" si="3"/>
-        <v>13.133333333333333</v>
-      </c>
-      <c r="K7">
-        <f t="shared" si="3"/>
-        <v>12.733333333333334</v>
+        <f t="shared" si="0"/>
+        <v>3.6</v>
+      </c>
+      <c r="K7" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="L7">
-        <f>AVERAGE(L4:L6)</f>
-        <v>0.15459999999999999</v>
+        <f t="shared" si="0"/>
+        <v>0.15433333333333332</v>
       </c>
       <c r="M7">
-        <f>AVERAGE(M4:M6)</f>
-        <v>5.1633333333333337E-2</v>
+        <f t="shared" si="0"/>
+        <v>4.5733333333333327E-2</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -14490,47 +14446,47 @@
       </c>
       <c r="B8">
         <f>_xlfn.STDEV.P(B4:B6)</f>
-        <v>0.18856180831641201</v>
-      </c>
-      <c r="C8">
-        <f t="shared" ref="C8:K8" si="4">_xlfn.STDEV.P(C4:C6)</f>
-        <v>0.18856180831641201</v>
+        <v>0</v>
+      </c>
+      <c r="C8" t="e">
+        <f t="shared" ref="C8:K8" si="1">_xlfn.STDEV.P(C4:C6)</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="D8">
-        <f t="shared" si="4"/>
-        <v>3.7416573867740237E-4</v>
+        <f t="shared" si="1"/>
+        <v>3.0291179500896805E-3</v>
       </c>
       <c r="E8">
-        <f t="shared" si="4"/>
-        <v>2.6246692913374042E-4</v>
+        <f t="shared" si="1"/>
+        <v>1.3490737563231915E-3</v>
       </c>
       <c r="F8">
-        <f t="shared" si="4"/>
-        <v>4.7140452079100489E-2</v>
-      </c>
-      <c r="G8">
-        <f t="shared" si="4"/>
-        <v>4.7140452079100489E-2</v>
+        <f t="shared" si="1"/>
+        <v>4.7140452079103841E-2</v>
+      </c>
+      <c r="G8" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="H8">
-        <f t="shared" si="4"/>
-        <v>2.1602468994692199E-4</v>
+        <f t="shared" si="1"/>
+        <v>5.9066817155565827E-4</v>
       </c>
       <c r="I8">
-        <f t="shared" si="4"/>
-        <v>1.2472191289245098E-4</v>
+        <f t="shared" si="1"/>
+        <v>1.235583532856711E-3</v>
       </c>
       <c r="J8">
-        <f t="shared" si="4"/>
-        <v>4.7140452079103001E-2</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="4"/>
-        <v>4.7140452079103001E-2</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K8" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="L8">
         <f>_xlfn.STDEV.P(L4:L6)</f>
-        <v>8.164965809277494E-5</v>
+        <v>3.7712361663282308E-4</v>
       </c>
       <c r="M8">
         <f>_xlfn.STDEV.P(M4:M6)</f>
@@ -14553,7 +14509,7 @@
         <v>69</v>
       </c>
       <c r="N11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -14561,7 +14517,7 @@
         <v>135</v>
       </c>
       <c r="C12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D12" t="s">
         <v>136</v>
@@ -14573,7 +14529,7 @@
         <v>135</v>
       </c>
       <c r="G12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H12" t="s">
         <v>136</v>
@@ -14585,7 +14541,7 @@
         <v>135</v>
       </c>
       <c r="K12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L12" t="s">
         <v>136</v>
@@ -14608,52 +14564,40 @@
         <v>1</v>
       </c>
       <c r="B13">
-        <v>7.2</v>
-      </c>
-      <c r="C13">
-        <f>B13-$N$13</f>
-        <v>7.1000000000000005</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="D13">
-        <v>0.62770000000000004</v>
+        <v>0.64500000000000002</v>
       </c>
       <c r="E13">
-        <v>0.32179999999999997</v>
+        <v>0.33239999999999997</v>
       </c>
       <c r="F13">
-        <v>31.7</v>
-      </c>
-      <c r="G13">
-        <f>F13-$N$13</f>
-        <v>31.599999999999998</v>
+        <v>71.7</v>
       </c>
       <c r="H13">
-        <v>0.29370000000000002</v>
+        <v>0.31890000000000002</v>
       </c>
       <c r="I13">
-        <v>0.58940000000000003</v>
+        <v>0.62309999999999999</v>
       </c>
       <c r="J13">
-        <v>3.2</v>
-      </c>
-      <c r="K13">
-        <f>J13-$N$13</f>
-        <v>3.1</v>
+        <v>6.9</v>
       </c>
       <c r="L13">
-        <v>0.15479999999999999</v>
+        <v>0.15240000000000001</v>
       </c>
       <c r="M13">
-        <v>4.7E-2</v>
+        <v>5.28E-2</v>
       </c>
       <c r="N13">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="O13">
-        <v>0.42099999999999999</v>
+        <v>0.21340000000000001</v>
       </c>
       <c r="P13">
-        <v>0.217</v>
+        <v>0.18429999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -14661,43 +14605,31 @@
         <v>2</v>
       </c>
       <c r="B14">
-        <v>7.3</v>
-      </c>
-      <c r="C14">
-        <f t="shared" ref="C14:C15" si="5">B14-$N$13</f>
-        <v>7.2</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="D14">
-        <v>0.62839999999999996</v>
+        <v>0.64500000000000002</v>
       </c>
       <c r="E14">
-        <v>0.32440000000000002</v>
+        <v>0.33160000000000001</v>
       </c>
       <c r="F14">
-        <v>31.7</v>
-      </c>
-      <c r="G14">
-        <f t="shared" ref="G14:G15" si="6">F14-$N$13</f>
-        <v>31.599999999999998</v>
+        <v>71.8</v>
       </c>
       <c r="H14">
-        <v>0.2954</v>
+        <v>0.31859999999999999</v>
       </c>
       <c r="I14">
-        <v>0.58909999999999996</v>
+        <v>0.62339999999999995</v>
       </c>
       <c r="J14">
-        <v>3.2</v>
-      </c>
-      <c r="K14">
-        <f t="shared" ref="K14:K15" si="7">J14-$N$13</f>
-        <v>3.1</v>
+        <v>7</v>
       </c>
       <c r="L14">
-        <v>0.15479999999999999</v>
+        <v>0.1525</v>
       </c>
       <c r="M14">
-        <v>4.65E-2</v>
+        <v>5.2699999999999997E-2</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -14705,43 +14637,31 @@
         <v>3</v>
       </c>
       <c r="B15">
-        <v>7.3</v>
-      </c>
-      <c r="C15">
-        <f>B15-$N$13</f>
-        <v>7.2</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="D15">
-        <v>0.63049999999999995</v>
+        <v>0.64439999999999997</v>
       </c>
       <c r="E15">
-        <v>0.32940000000000003</v>
+        <v>0.33210000000000001</v>
       </c>
       <c r="F15">
-        <v>31.7</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="6"/>
-        <v>31.599999999999998</v>
+        <v>71.900000000000006</v>
       </c>
       <c r="H15">
-        <v>0.29370000000000002</v>
+        <v>0.31979999999999997</v>
       </c>
       <c r="I15">
-        <v>0.58919999999999995</v>
+        <v>0.62290000000000001</v>
       </c>
       <c r="J15">
-        <v>3.2</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="7"/>
-        <v>3.1</v>
+        <v>7</v>
       </c>
       <c r="L15">
-        <v>0.15459999999999999</v>
+        <v>0.1525</v>
       </c>
       <c r="M15">
-        <v>4.6600000000000003E-2</v>
+        <v>5.2600000000000001E-2</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -14750,730 +14670,104 @@
       </c>
       <c r="B16">
         <f>AVERAGE(B13:B15)</f>
-        <v>7.2666666666666666</v>
-      </c>
-      <c r="C16">
-        <f t="shared" ref="C16:K16" si="8">AVERAGE(C13:C15)</f>
-        <v>7.166666666666667</v>
+        <v>19.899999999999999</v>
+      </c>
+      <c r="C16" t="e">
+        <f t="shared" ref="C16:K16" si="2">AVERAGE(C13:C15)</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="D16">
-        <f t="shared" si="8"/>
-        <v>0.62886666666666668</v>
+        <f t="shared" si="2"/>
+        <v>0.64480000000000004</v>
       </c>
       <c r="E16">
-        <f t="shared" si="8"/>
-        <v>0.32519999999999999</v>
+        <f t="shared" si="2"/>
+        <v>0.33203333333333335</v>
       </c>
       <c r="F16">
-        <f t="shared" si="8"/>
-        <v>31.7</v>
-      </c>
-      <c r="G16">
-        <f t="shared" si="8"/>
-        <v>31.599999999999998</v>
+        <f t="shared" si="2"/>
+        <v>71.8</v>
+      </c>
+      <c r="G16" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="H16">
-        <f t="shared" si="8"/>
-        <v>0.29426666666666668</v>
+        <f t="shared" si="2"/>
+        <v>0.31909999999999999</v>
       </c>
       <c r="I16">
-        <f t="shared" si="8"/>
-        <v>0.58923333333333339</v>
+        <f t="shared" si="2"/>
+        <v>0.62313333333333332</v>
       </c>
       <c r="J16">
-        <f t="shared" si="8"/>
-        <v>3.2000000000000006</v>
-      </c>
-      <c r="K16">
-        <f t="shared" si="8"/>
-        <v>3.1</v>
+        <f t="shared" si="2"/>
+        <v>6.9666666666666659</v>
+      </c>
+      <c r="K16" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="L16">
         <f>AVERAGE(L13:L15)</f>
-        <v>0.15473333333333331</v>
+        <v>0.15246666666666667</v>
       </c>
       <c r="M16">
         <f>AVERAGE(M13:M15)</f>
-        <v>4.6699999999999998E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16">
+        <v>5.2699999999999997E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" t="s">
         <v>134</v>
       </c>
       <c r="B17">
         <f>_xlfn.STDEV.P(B13:B15)</f>
+        <v>0</v>
+      </c>
+      <c r="C17" t="e">
+        <f t="shared" ref="C17:K17" si="3">_xlfn.STDEV.P(C13:C15)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="3"/>
+        <v>2.8284271247464021E-4</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="3"/>
+        <v>3.2998316455371012E-4</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="3"/>
+        <v>8.1649658092773761E-2</v>
+      </c>
+      <c r="G17" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="3"/>
+        <v>5.0990195135926588E-4</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="3"/>
+        <v>2.0548046676560993E-4</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="3"/>
         <v>4.7140452079103001E-2</v>
       </c>
-      <c r="C17">
-        <f t="shared" ref="C17:K17" si="9">_xlfn.STDEV.P(C13:C15)</f>
-        <v>4.7140452079103001E-2</v>
-      </c>
-      <c r="D17">
-        <f t="shared" si="9"/>
-        <v>1.189771219838287E-3</v>
-      </c>
-      <c r="E17">
-        <f t="shared" si="9"/>
-        <v>3.1538336460039847E-3</v>
-      </c>
-      <c r="F17">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <f t="shared" si="9"/>
-        <v>8.0138768534474415E-4</v>
-      </c>
-      <c r="I17">
-        <f t="shared" si="9"/>
-        <v>1.2472191289250044E-4</v>
-      </c>
-      <c r="J17">
-        <f t="shared" si="9"/>
-        <v>4.4408920985006262E-16</v>
-      </c>
-      <c r="K17">
-        <f t="shared" si="9"/>
-        <v>0</v>
+      <c r="K17" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="L17">
         <f>_xlfn.STDEV.P(L13:L15)</f>
-        <v>9.4280904158209036E-5</v>
+        <v>4.7140452079097985E-5</v>
       </c>
       <c r="M17">
         <f>_xlfn.STDEV.P(M13:M15)</f>
-        <v>2.1602468994692844E-4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16">
-      <c r="A19" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16">
-      <c r="B20" t="s">
-        <v>67</v>
-      </c>
-      <c r="F20" t="s">
-        <v>68</v>
-      </c>
-      <c r="J20" t="s">
-        <v>69</v>
-      </c>
-      <c r="N20" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16">
-      <c r="B21" t="s">
-        <v>135</v>
-      </c>
-      <c r="C21" t="s">
-        <v>143</v>
-      </c>
-      <c r="D21" t="s">
-        <v>136</v>
-      </c>
-      <c r="E21" t="s">
-        <v>137</v>
-      </c>
-      <c r="F21" t="s">
-        <v>135</v>
-      </c>
-      <c r="G21" t="s">
-        <v>143</v>
-      </c>
-      <c r="H21" t="s">
-        <v>136</v>
-      </c>
-      <c r="I21" t="s">
-        <v>137</v>
-      </c>
-      <c r="J21" t="s">
-        <v>135</v>
-      </c>
-      <c r="K21" t="s">
-        <v>143</v>
-      </c>
-      <c r="L21" t="s">
-        <v>136</v>
-      </c>
-      <c r="M21" t="s">
-        <v>137</v>
-      </c>
-      <c r="N21" t="s">
-        <v>135</v>
-      </c>
-      <c r="O21" t="s">
-        <v>136</v>
-      </c>
-      <c r="P21" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16">
-      <c r="A22">
-        <v>1</v>
-      </c>
-      <c r="B22">
-        <v>30.7</v>
-      </c>
-      <c r="C22">
-        <f>B22-$N$22</f>
-        <v>30.4</v>
-      </c>
-      <c r="D22">
-        <v>0.65690000000000004</v>
-      </c>
-      <c r="E22">
-        <v>0.3201</v>
-      </c>
-      <c r="F22">
-        <v>114.5</v>
-      </c>
-      <c r="G22">
-        <f>F22-$N$22</f>
-        <v>114.2</v>
-      </c>
-      <c r="H22">
-        <v>0.3276</v>
-      </c>
-      <c r="I22">
-        <v>0.61439999999999995</v>
-      </c>
-      <c r="J22">
-        <v>11.5</v>
-      </c>
-      <c r="K22">
-        <f>J22-$N$22</f>
-        <v>11.2</v>
-      </c>
-      <c r="L22">
-        <v>0.15659999999999999</v>
-      </c>
-      <c r="M22">
-        <v>4.8899999999999999E-2</v>
-      </c>
-      <c r="N22">
-        <v>0.3</v>
-      </c>
-      <c r="O22">
-        <v>0.2702</v>
-      </c>
-      <c r="P22">
-        <v>0.26229999999999998</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16">
-      <c r="A23">
-        <v>2</v>
-      </c>
-      <c r="B23">
-        <v>30.8</v>
-      </c>
-      <c r="C23">
-        <f t="shared" ref="C23:C24" si="10">B23-$N$22</f>
-        <v>30.5</v>
-      </c>
-      <c r="D23">
-        <v>0.65800000000000003</v>
-      </c>
-      <c r="E23">
-        <v>0.32040000000000002</v>
-      </c>
-      <c r="F23">
-        <v>114</v>
-      </c>
-      <c r="G23">
-        <f t="shared" ref="G23:G24" si="11">F23-$N$22</f>
-        <v>113.7</v>
-      </c>
-      <c r="H23">
-        <v>0.32969999999999999</v>
-      </c>
-      <c r="I23">
-        <v>0.61380000000000001</v>
-      </c>
-      <c r="J23">
-        <v>11.5</v>
-      </c>
-      <c r="K23">
-        <f t="shared" ref="K23:K24" si="12">J23-$N$22</f>
-        <v>11.2</v>
-      </c>
-      <c r="L23">
-        <v>0.1598</v>
-      </c>
-      <c r="M23">
-        <v>4.99E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16">
-      <c r="A24">
-        <v>3</v>
-      </c>
-      <c r="B24">
-        <v>30.9</v>
-      </c>
-      <c r="C24">
-        <f t="shared" si="10"/>
-        <v>30.599999999999998</v>
-      </c>
-      <c r="D24">
-        <v>0.65610000000000002</v>
-      </c>
-      <c r="E24">
-        <v>0.32129999999999997</v>
-      </c>
-      <c r="F24">
-        <v>114.4</v>
-      </c>
-      <c r="G24">
-        <f t="shared" si="11"/>
-        <v>114.10000000000001</v>
-      </c>
-      <c r="H24">
-        <v>0.32969999999999999</v>
-      </c>
-      <c r="I24">
-        <v>0.61380000000000001</v>
-      </c>
-      <c r="J24">
-        <v>11.4</v>
-      </c>
-      <c r="K24">
-        <f t="shared" si="12"/>
-        <v>11.1</v>
-      </c>
-      <c r="L24">
-        <v>0.16220000000000001</v>
-      </c>
-      <c r="M24">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16">
-      <c r="A25" t="s">
-        <v>86</v>
-      </c>
-      <c r="B25">
-        <f>AVERAGE(B22:B24)</f>
-        <v>30.8</v>
-      </c>
-      <c r="C25">
-        <f t="shared" ref="C25:K25" si="13">AVERAGE(C22:C24)</f>
-        <v>30.5</v>
-      </c>
-      <c r="D25">
-        <f t="shared" si="13"/>
-        <v>0.65700000000000003</v>
-      </c>
-      <c r="E25">
-        <f t="shared" si="13"/>
-        <v>0.3206</v>
-      </c>
-      <c r="F25">
-        <f t="shared" si="13"/>
-        <v>114.3</v>
-      </c>
-      <c r="G25">
-        <f t="shared" si="13"/>
-        <v>114</v>
-      </c>
-      <c r="H25">
-        <f t="shared" si="13"/>
-        <v>0.32900000000000001</v>
-      </c>
-      <c r="I25">
-        <f t="shared" si="13"/>
-        <v>0.61399999999999999</v>
-      </c>
-      <c r="J25">
-        <f t="shared" si="13"/>
-        <v>11.466666666666667</v>
-      </c>
-      <c r="K25">
-        <f t="shared" si="13"/>
-        <v>11.166666666666666</v>
-      </c>
-      <c r="L25">
-        <f>AVERAGE(L22:L24)</f>
-        <v>0.15953333333333333</v>
-      </c>
-      <c r="M25">
-        <f>AVERAGE(M22:M24)</f>
-        <v>4.9599999999999998E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16">
-      <c r="A26" t="s">
-        <v>134</v>
-      </c>
-      <c r="B26">
-        <f>_xlfn.STDEV.P(B22:B24)</f>
-        <v>8.1649658092772318E-2</v>
-      </c>
-      <c r="C26">
-        <f t="shared" ref="C26:K26" si="14">_xlfn.STDEV.P(C22:C24)</f>
-        <v>8.1649658092772318E-2</v>
-      </c>
-      <c r="D26">
-        <f t="shared" si="14"/>
-        <v>7.7888809636986601E-4</v>
-      </c>
-      <c r="E26">
-        <f t="shared" si="14"/>
-        <v>5.0990195135926588E-4</v>
-      </c>
-      <c r="F26">
-        <f t="shared" si="14"/>
-        <v>0.21602468994692955</v>
-      </c>
-      <c r="G26">
-        <f t="shared" si="14"/>
-        <v>0.21602468994692955</v>
-      </c>
-      <c r="H26">
-        <f t="shared" si="14"/>
-        <v>9.8994949366116225E-4</v>
-      </c>
-      <c r="I26">
-        <f t="shared" si="14"/>
-        <v>2.828427124745879E-4</v>
-      </c>
-      <c r="J26">
-        <f t="shared" si="14"/>
-        <v>4.7140452079103001E-2</v>
-      </c>
-      <c r="K26">
-        <f t="shared" si="14"/>
-        <v>4.7140452079103001E-2</v>
-      </c>
-      <c r="L26">
-        <f>_xlfn.STDEV.P(L22:L24)</f>
-        <v>2.2939534045447094E-3</v>
-      </c>
-      <c r="M26">
-        <f>_xlfn.STDEV.P(M22:M24)</f>
-        <v>4.9665548085837919E-4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16">
-      <c r="A28" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16">
-      <c r="B29" t="s">
-        <v>67</v>
-      </c>
-      <c r="F29" t="s">
-        <v>68</v>
-      </c>
-      <c r="J29" t="s">
-        <v>69</v>
-      </c>
-      <c r="N29" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16">
-      <c r="B30" t="s">
-        <v>135</v>
-      </c>
-      <c r="C30" t="s">
-        <v>143</v>
-      </c>
-      <c r="D30" t="s">
-        <v>136</v>
-      </c>
-      <c r="E30" t="s">
-        <v>137</v>
-      </c>
-      <c r="F30" t="s">
-        <v>135</v>
-      </c>
-      <c r="G30" t="s">
-        <v>143</v>
-      </c>
-      <c r="H30" t="s">
-        <v>136</v>
-      </c>
-      <c r="I30" t="s">
-        <v>137</v>
-      </c>
-      <c r="J30" t="s">
-        <v>135</v>
-      </c>
-      <c r="K30" t="s">
-        <v>143</v>
-      </c>
-      <c r="L30" t="s">
-        <v>136</v>
-      </c>
-      <c r="M30" t="s">
-        <v>137</v>
-      </c>
-      <c r="N30" t="s">
-        <v>135</v>
-      </c>
-      <c r="O30" t="s">
-        <v>136</v>
-      </c>
-      <c r="P30" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16">
-      <c r="A31">
-        <v>1</v>
-      </c>
-      <c r="B31">
-        <v>20.399999999999999</v>
-      </c>
-      <c r="C31">
-        <f>B31-$N$31</f>
-        <v>20.2</v>
-      </c>
-      <c r="D31">
-        <v>0.64349999999999996</v>
-      </c>
-      <c r="E31">
-        <v>0.33229999999999998</v>
-      </c>
-      <c r="F31">
-        <v>73.7</v>
-      </c>
-      <c r="G31">
-        <f>F31-$N$31</f>
-        <v>73.5</v>
-      </c>
-      <c r="H31">
-        <v>0.31950000000000001</v>
-      </c>
-      <c r="I31">
-        <v>0.62309999999999999</v>
-      </c>
-      <c r="J31">
-        <v>7</v>
-      </c>
-      <c r="K31">
-        <f>J31-$N$31</f>
-        <v>6.8</v>
-      </c>
-      <c r="L31">
-        <v>0.15279999999999999</v>
-      </c>
-      <c r="M31">
-        <v>5.1499999999999997E-2</v>
-      </c>
-      <c r="N31">
-        <v>0.2</v>
-      </c>
-      <c r="O31">
-        <v>0.21340000000000001</v>
-      </c>
-      <c r="P31">
-        <v>0.18429999999999999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16">
-      <c r="A32">
-        <v>2</v>
-      </c>
-      <c r="B32">
-        <v>20.3</v>
-      </c>
-      <c r="C32">
-        <f t="shared" ref="C32:C33" si="15">B32-$N$31</f>
-        <v>20.100000000000001</v>
-      </c>
-      <c r="D32">
-        <v>0.64549999999999996</v>
-      </c>
-      <c r="E32">
-        <v>0.33260000000000001</v>
-      </c>
-      <c r="F32">
-        <v>73.7</v>
-      </c>
-      <c r="G32">
-        <f t="shared" ref="G32:G33" si="16">F32-$N$31</f>
-        <v>73.5</v>
-      </c>
-      <c r="H32">
-        <v>0.32</v>
-      </c>
-      <c r="I32">
-        <v>0.62460000000000004</v>
-      </c>
-      <c r="J32">
-        <v>7</v>
-      </c>
-      <c r="K32">
-        <f t="shared" ref="K32:K33" si="17">J32-$N$31</f>
-        <v>6.8</v>
-      </c>
-      <c r="L32">
-        <v>0.1527</v>
-      </c>
-      <c r="M32">
-        <v>5.1299999999999998E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13">
-      <c r="A33">
-        <v>3</v>
-      </c>
-      <c r="B33">
-        <v>20.3</v>
-      </c>
-      <c r="C33">
-        <f t="shared" si="15"/>
-        <v>20.100000000000001</v>
-      </c>
-      <c r="D33">
-        <v>0.64610000000000001</v>
-      </c>
-      <c r="E33">
-        <v>0.33239999999999997</v>
-      </c>
-      <c r="F33">
-        <v>73.7</v>
-      </c>
-      <c r="G33">
-        <f t="shared" si="16"/>
-        <v>73.5</v>
-      </c>
-      <c r="H33">
-        <v>0.31890000000000002</v>
-      </c>
-      <c r="I33">
-        <v>0.62370000000000003</v>
-      </c>
-      <c r="J33">
-        <v>7</v>
-      </c>
-      <c r="K33">
-        <f t="shared" si="17"/>
-        <v>6.8</v>
-      </c>
-      <c r="L33">
-        <v>0.15179999999999999</v>
-      </c>
-      <c r="M33">
-        <v>5.1700000000000003E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13">
-      <c r="A34" t="s">
-        <v>86</v>
-      </c>
-      <c r="B34">
-        <f>AVERAGE(B31:B33)</f>
-        <v>20.333333333333332</v>
-      </c>
-      <c r="C34">
-        <f t="shared" ref="C34:K34" si="18">AVERAGE(C31:C33)</f>
-        <v>20.133333333333333</v>
-      </c>
-      <c r="D34">
-        <f t="shared" si="18"/>
-        <v>0.64503333333333324</v>
-      </c>
-      <c r="E34">
-        <f t="shared" si="18"/>
-        <v>0.33243333333333336</v>
-      </c>
-      <c r="F34">
-        <f t="shared" si="18"/>
-        <v>73.7</v>
-      </c>
-      <c r="G34">
-        <f t="shared" si="18"/>
-        <v>73.5</v>
-      </c>
-      <c r="H34">
-        <f t="shared" si="18"/>
-        <v>0.31946666666666662</v>
-      </c>
-      <c r="I34">
-        <f t="shared" si="18"/>
-        <v>0.62380000000000002</v>
-      </c>
-      <c r="J34">
-        <f t="shared" si="18"/>
-        <v>7</v>
-      </c>
-      <c r="K34">
-        <f t="shared" si="18"/>
-        <v>6.8</v>
-      </c>
-      <c r="L34">
-        <f>AVERAGE(L31:L33)</f>
-        <v>0.15243333333333334</v>
-      </c>
-      <c r="M34">
-        <f>AVERAGE(M31:M33)</f>
-        <v>5.1499999999999997E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
-      <c r="A35" t="s">
-        <v>134</v>
-      </c>
-      <c r="B35">
-        <f>_xlfn.STDEV.P(B31:B33)</f>
-        <v>4.7140452079102169E-2</v>
-      </c>
-      <c r="C35">
-        <f t="shared" ref="C35:K35" si="19">_xlfn.STDEV.P(C31:C33)</f>
-        <v>4.7140452079102169E-2</v>
-      </c>
-      <c r="D35">
-        <f t="shared" si="19"/>
-        <v>1.1115554667022196E-3</v>
-      </c>
-      <c r="E35">
-        <f t="shared" si="19"/>
-        <v>1.247219128924757E-4</v>
-      </c>
-      <c r="F35">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="G35">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <f t="shared" si="19"/>
-        <v>4.4969125210773047E-4</v>
-      </c>
-      <c r="I35">
-        <f t="shared" si="19"/>
-        <v>6.1644140029691976E-4</v>
-      </c>
-      <c r="J35">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="K35">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="L35">
-        <f>_xlfn.STDEV.P(L31:L33)</f>
-        <v>4.496912521077373E-4</v>
-      </c>
-      <c r="M35">
-        <f>_xlfn.STDEV.P(M31:M33)</f>
-        <v>1.6329931618554703E-4</v>
+        <v>8.1649658092772107E-5</v>
       </c>
     </row>
   </sheetData>
